--- a/SubRES_Tmpl/SubRES_Conventional_Trans.xlsx
+++ b/SubRES_Tmpl/SubRES_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VS_CEA_8C\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B8F2B9C-406B-4B10-B8AD-AE2C1EA2ADC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{142A000A-77BB-43B2-A431-2E98DE174023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="2940" windowWidth="21600" windowHeight="12772" activeTab="9" xr2:uid="{B3A632FA-6C2C-431D-8B81-9269161175AD}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="12773" activeTab="9" xr2:uid="{51632895-78B1-4A7F-9BE1-79180EB78936}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA_FRA" sheetId="2" r:id="rId1"/>
@@ -92,67 +92,175 @@
     <t>EN_STG8hbNREL,EN_STG4hbNREL</t>
   </si>
   <si>
+    <t>Caen_FRA</t>
+  </si>
+  <si>
+    <t>at grid node - Caen_FRA</t>
+  </si>
+  <si>
+    <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
+  </si>
+  <si>
+    <t>h_demand</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler,en_hop_biomass_chips,en_hop_electric_boiler,en_hp_air_10mw</t>
+  </si>
+  <si>
+    <t>Bordeaux_FRA</t>
+  </si>
+  <si>
+    <t>at grid node - Bordeaux_FRA</t>
+  </si>
+  <si>
+    <t>Goussainville_FRA</t>
+  </si>
+  <si>
+    <t>at grid node - Goussainville_FRA</t>
+  </si>
+  <si>
+    <t>CharlevilleMeziere_FRA</t>
+  </si>
+  <si>
+    <t>at grid node - CharlevilleMeziere_FRA</t>
+  </si>
+  <si>
+    <t>Mohon_FRA</t>
+  </si>
+  <si>
+    <t>at grid node - Mohon_FRA</t>
+  </si>
+  <si>
+    <t>Bastia_FRA</t>
+  </si>
+  <si>
+    <t>at grid node - Bastia_FRA</t>
+  </si>
+  <si>
+    <t>Bayonne_FRA</t>
+  </si>
+  <si>
+    <t>at grid node - Bayonne_FRA</t>
+  </si>
+  <si>
+    <t>Rouen_FRA</t>
+  </si>
+  <si>
+    <t>at grid node - Rouen_FRA</t>
+  </si>
+  <si>
+    <t>Nimes_FRA</t>
+  </si>
+  <si>
+    <t>at grid node - Nimes_FRA</t>
+  </si>
+  <si>
+    <t>Aurillac_FRA</t>
+  </si>
+  <si>
+    <t>at grid node - Aurillac_FRA</t>
+  </si>
+  <si>
+    <t>Lyon_FRA</t>
+  </si>
+  <si>
+    <t>at grid node - Lyon_FRA</t>
+  </si>
+  <si>
+    <t>Nice_FRA</t>
+  </si>
+  <si>
+    <t>at grid node - Nice_FRA</t>
+  </si>
+  <si>
+    <t>Toulouse_FRA</t>
+  </si>
+  <si>
+    <t>at grid node - Toulouse_FRA</t>
+  </si>
+  <si>
+    <t>Belfort_FRA</t>
+  </si>
+  <si>
+    <t>at grid node - Belfort_FRA</t>
+  </si>
+  <si>
+    <t>AixLesBains_FRA</t>
+  </si>
+  <si>
+    <t>at grid node - AixLesBains_FRA</t>
+  </si>
+  <si>
+    <t>Perpignan_FRA</t>
+  </si>
+  <si>
+    <t>at grid node - Perpignan_FRA</t>
+  </si>
+  <si>
+    <t>Metz_FRA</t>
+  </si>
+  <si>
+    <t>at grid node - Metz_FRA</t>
+  </si>
+  <si>
+    <t>ThononLesBains_FRA</t>
+  </si>
+  <si>
+    <t>at grid node - ThononLesBains_FRA</t>
+  </si>
+  <si>
+    <t>Strasbourg_FRA</t>
+  </si>
+  <si>
+    <t>at grid node - Strasbourg_FRA</t>
+  </si>
+  <si>
+    <t>Thionville_FRA</t>
+  </si>
+  <si>
+    <t>at grid node - Thionville_FRA</t>
+  </si>
+  <si>
+    <t>Dunkerque_FRA</t>
+  </si>
+  <si>
+    <t>at grid node - Dunkerque_FRA</t>
+  </si>
+  <si>
+    <t>Brest_FRA</t>
+  </si>
+  <si>
+    <t>at grid node - Brest_FRA</t>
+  </si>
+  <si>
+    <t>Lille_FRA</t>
+  </si>
+  <si>
+    <t>at grid node - Lille_FRA</t>
+  </si>
+  <si>
     <t>Forbach_FRA</t>
   </si>
   <si>
     <t>at grid node - Forbach_FRA</t>
   </si>
   <si>
-    <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
-  </si>
-  <si>
-    <t>h_demand</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler,en_hop_biomass_chips,en_hop_electric_boiler,en_hp_air_10mw</t>
-  </si>
-  <si>
-    <t>Bordeaux_FRA</t>
-  </si>
-  <si>
-    <t>at grid node - Bordeaux_FRA</t>
-  </si>
-  <si>
-    <t>Goussainville_FRA</t>
-  </si>
-  <si>
-    <t>at grid node - Goussainville_FRA</t>
-  </si>
-  <si>
-    <t>Bayonne_FRA</t>
-  </si>
-  <si>
-    <t>at grid node - Bayonne_FRA</t>
-  </si>
-  <si>
-    <t>Mohon_FRA</t>
-  </si>
-  <si>
-    <t>at grid node - Mohon_FRA</t>
-  </si>
-  <si>
-    <t>Bastia_FRA</t>
-  </si>
-  <si>
-    <t>at grid node - Bastia_FRA</t>
-  </si>
-  <si>
     <t>Mulhouse_FRA</t>
   </si>
   <si>
     <t>at grid node - Mulhouse_FRA</t>
   </si>
   <si>
-    <t>Rouen_FRA</t>
-  </si>
-  <si>
-    <t>at grid node - Rouen_FRA</t>
-  </si>
-  <si>
-    <t>Nimes_FRA</t>
-  </si>
-  <si>
-    <t>at grid node - Nimes_FRA</t>
+    <t>Lourdes_FRA</t>
+  </si>
+  <si>
+    <t>at grid node - Lourdes_FRA</t>
+  </si>
+  <si>
+    <t>Nantes_FRA</t>
+  </si>
+  <si>
+    <t>at grid node - Nantes_FRA</t>
   </si>
   <si>
     <t>Dijon_FRA</t>
@@ -161,88 +269,22 @@
     <t>at grid node - Dijon_FRA</t>
   </si>
   <si>
-    <t>Lyon_FRA</t>
-  </si>
-  <si>
-    <t>at grid node - Lyon_FRA</t>
-  </si>
-  <si>
-    <t>Nice_FRA</t>
-  </si>
-  <si>
-    <t>at grid node - Nice_FRA</t>
-  </si>
-  <si>
-    <t>Lourdes_FRA</t>
-  </si>
-  <si>
-    <t>at grid node - Lourdes_FRA</t>
-  </si>
-  <si>
-    <t>Toulouse_FRA</t>
-  </si>
-  <si>
-    <t>at grid node - Toulouse_FRA</t>
-  </si>
-  <si>
-    <t>Belfort_FRA</t>
-  </si>
-  <si>
-    <t>at grid node - Belfort_FRA</t>
-  </si>
-  <si>
-    <t>CharlevilleMeziere_FRA</t>
-  </si>
-  <si>
-    <t>at grid node - CharlevilleMeziere_FRA</t>
-  </si>
-  <si>
-    <t>Perpignan_FRA</t>
-  </si>
-  <si>
-    <t>at grid node - Perpignan_FRA</t>
-  </si>
-  <si>
-    <t>Metz_FRA</t>
-  </si>
-  <si>
-    <t>at grid node - Metz_FRA</t>
-  </si>
-  <si>
-    <t>Strasbourg_FRA</t>
-  </si>
-  <si>
-    <t>at grid node - Strasbourg_FRA</t>
-  </si>
-  <si>
-    <t>Caen_FRA</t>
-  </si>
-  <si>
-    <t>at grid node - Caen_FRA</t>
-  </si>
-  <si>
-    <t>Lille_FRA</t>
-  </si>
-  <si>
-    <t>at grid node - Lille_FRA</t>
-  </si>
-  <si>
-    <t>Dunkerque_FRA</t>
-  </si>
-  <si>
-    <t>at grid node - Dunkerque_FRA</t>
-  </si>
-  <si>
-    <t>Brest_FRA</t>
-  </si>
-  <si>
-    <t>at grid node - Brest_FRA</t>
-  </si>
-  <si>
-    <t>Aurillac_FRA</t>
-  </si>
-  <si>
-    <t>at grid node - Aurillac_FRA</t>
+    <t>Haguenau_FRA</t>
+  </si>
+  <si>
+    <t>at grid node - Haguenau_FRA</t>
+  </si>
+  <si>
+    <t>Annecy_FRA</t>
+  </si>
+  <si>
+    <t>at grid node - Annecy_FRA</t>
+  </si>
+  <si>
+    <t>Calais_FRA</t>
+  </si>
+  <si>
+    <t>at grid node - Calais_FRA</t>
   </si>
   <si>
     <t>Briancon_FRA</t>
@@ -251,48 +293,6 @@
     <t>at grid node - Briancon_FRA</t>
   </si>
   <si>
-    <t>Thionville_FRA</t>
-  </si>
-  <si>
-    <t>at grid node - Thionville_FRA</t>
-  </si>
-  <si>
-    <t>Nantes_FRA</t>
-  </si>
-  <si>
-    <t>at grid node - Nantes_FRA</t>
-  </si>
-  <si>
-    <t>AixLesBains_FRA</t>
-  </si>
-  <si>
-    <t>at grid node - AixLesBains_FRA</t>
-  </si>
-  <si>
-    <t>Calais_FRA</t>
-  </si>
-  <si>
-    <t>at grid node - Calais_FRA</t>
-  </si>
-  <si>
-    <t>ThononLesBains_FRA</t>
-  </si>
-  <si>
-    <t>at grid node - ThononLesBains_FRA</t>
-  </si>
-  <si>
-    <t>Annecy_FRA</t>
-  </si>
-  <si>
-    <t>at grid node - Annecy_FRA</t>
-  </si>
-  <si>
-    <t>Haguenau_FRA</t>
-  </si>
-  <si>
-    <t>at grid node - Haguenau_FRA</t>
-  </si>
-  <si>
     <t>GBR</t>
   </si>
   <si>
@@ -308,22 +308,40 @@
     <t>at grid node - Basildon_GBR</t>
   </si>
   <si>
+    <t>Portsmouth_GBR</t>
+  </si>
+  <si>
+    <t>at grid node - Portsmouth_GBR</t>
+  </si>
+  <si>
+    <t>Peterborough_GBR</t>
+  </si>
+  <si>
+    <t>at grid node - Peterborough_GBR</t>
+  </si>
+  <si>
+    <t>Liverpool_GBR</t>
+  </si>
+  <si>
+    <t>at grid node - Liverpool_GBR</t>
+  </si>
+  <si>
+    <t>Lerwick_GBR</t>
+  </si>
+  <si>
+    <t>at grid node - Lerwick_GBR</t>
+  </si>
+  <si>
     <t>Ipswich_GBR</t>
   </si>
   <si>
     <t>at grid node - Ipswich_GBR</t>
   </si>
   <si>
-    <t>Peterborough_GBR</t>
-  </si>
-  <si>
-    <t>at grid node - Peterborough_GBR</t>
-  </si>
-  <si>
-    <t>Liverpool_GBR</t>
-  </si>
-  <si>
-    <t>at grid node - Liverpool_GBR</t>
+    <t>Paisley_GBR</t>
+  </si>
+  <si>
+    <t>at grid node - Paisley_GBR</t>
   </si>
   <si>
     <t>Aberdeen_GBR</t>
@@ -332,16 +350,10 @@
     <t>at grid node - Aberdeen_GBR</t>
   </si>
   <si>
-    <t>Portsmouth_GBR</t>
-  </si>
-  <si>
-    <t>at grid node - Portsmouth_GBR</t>
-  </si>
-  <si>
-    <t>Paisley_GBR</t>
-  </si>
-  <si>
-    <t>at grid node - Paisley_GBR</t>
+    <t>Elgin_GBR</t>
+  </si>
+  <si>
+    <t>at grid node - Elgin_GBR</t>
   </si>
   <si>
     <t>Belfast_GBR</t>
@@ -350,36 +362,24 @@
     <t>at grid node - Belfast_GBR</t>
   </si>
   <si>
-    <t>Elgin_GBR</t>
-  </si>
-  <si>
-    <t>at grid node - Elgin_GBR</t>
-  </si>
-  <si>
     <t>Lisburn_GBR</t>
   </si>
   <si>
     <t>at grid node - Lisburn_GBR</t>
   </si>
   <si>
+    <t>Ashford_GBR</t>
+  </si>
+  <si>
+    <t>at grid node - Ashford_GBR</t>
+  </si>
+  <si>
     <t>Stranraer_GBR</t>
   </si>
   <si>
     <t>at grid node - Stranraer_GBR</t>
   </si>
   <si>
-    <t>Ashford_GBR</t>
-  </si>
-  <si>
-    <t>at grid node - Ashford_GBR</t>
-  </si>
-  <si>
-    <t>Lerwick_GBR</t>
-  </si>
-  <si>
-    <t>at grid node - Lerwick_GBR</t>
-  </si>
-  <si>
     <t>Wick_GBR</t>
   </si>
   <si>
@@ -401,60 +401,60 @@
     <t>at grid node - Gent_BEL</t>
   </si>
   <si>
+    <t>Arlon_BEL</t>
+  </si>
+  <si>
+    <t>at grid node - Arlon_BEL</t>
+  </si>
+  <si>
+    <t>Brussels_BEL</t>
+  </si>
+  <si>
+    <t>at grid node - Brussels_BEL</t>
+  </si>
+  <si>
+    <t>Namur_BEL</t>
+  </si>
+  <si>
+    <t>at grid node - Namur_BEL</t>
+  </si>
+  <si>
+    <t>Charleroi_BEL</t>
+  </si>
+  <si>
+    <t>at grid node - Charleroi_BEL</t>
+  </si>
+  <si>
+    <t>Seraing_BEL</t>
+  </si>
+  <si>
+    <t>at grid node - Seraing_BEL</t>
+  </si>
+  <si>
+    <t>Bruges_BEL</t>
+  </si>
+  <si>
+    <t>at grid node - Bruges_BEL</t>
+  </si>
+  <si>
+    <t>Hasselt_BEL</t>
+  </si>
+  <si>
+    <t>at grid node - Hasselt_BEL</t>
+  </si>
+  <si>
+    <t>Kortrijk_BEL</t>
+  </si>
+  <si>
+    <t>at grid node - Kortrijk_BEL</t>
+  </si>
+  <si>
     <t>Aubange_BEL</t>
   </si>
   <si>
     <t>at grid node - Aubange_BEL</t>
   </si>
   <si>
-    <t>Brussels_BEL</t>
-  </si>
-  <si>
-    <t>at grid node - Brussels_BEL</t>
-  </si>
-  <si>
-    <t>Seraing_BEL</t>
-  </si>
-  <si>
-    <t>at grid node - Seraing_BEL</t>
-  </si>
-  <si>
-    <t>Charleroi_BEL</t>
-  </si>
-  <si>
-    <t>at grid node - Charleroi_BEL</t>
-  </si>
-  <si>
-    <t>Arlon_BEL</t>
-  </si>
-  <si>
-    <t>at grid node - Arlon_BEL</t>
-  </si>
-  <si>
-    <t>Bruges_BEL</t>
-  </si>
-  <si>
-    <t>at grid node - Bruges_BEL</t>
-  </si>
-  <si>
-    <t>Kortrijk_BEL</t>
-  </si>
-  <si>
-    <t>at grid node - Kortrijk_BEL</t>
-  </si>
-  <si>
-    <t>Hasselt_BEL</t>
-  </si>
-  <si>
-    <t>at grid node - Hasselt_BEL</t>
-  </si>
-  <si>
-    <t>Namur_BEL</t>
-  </si>
-  <si>
-    <t>at grid node - Namur_BEL</t>
-  </si>
-  <si>
     <t>DEU</t>
   </si>
   <si>
@@ -470,22 +470,202 @@
     <t>at grid node - Amberg_DEU</t>
   </si>
   <si>
+    <t>SchwedtOder_DEU</t>
+  </si>
+  <si>
+    <t>at grid node - SchwedtOder_DEU</t>
+  </si>
+  <si>
+    <t>Rheine_DEU</t>
+  </si>
+  <si>
+    <t>at grid node - Rheine_DEU</t>
+  </si>
+  <si>
+    <t>Cologne_DEU</t>
+  </si>
+  <si>
+    <t>at grid node - Cologne_DEU</t>
+  </si>
+  <si>
+    <t>Ravensburg_DEU</t>
+  </si>
+  <si>
+    <t>at grid node - Ravensburg_DEU</t>
+  </si>
+  <si>
+    <t>Emden_DEU</t>
+  </si>
+  <si>
+    <t>at grid node - Emden_DEU</t>
+  </si>
+  <si>
+    <t>Ulm_DEU</t>
+  </si>
+  <si>
+    <t>at grid node - Ulm_DEU</t>
+  </si>
+  <si>
+    <t>Wurzburg_DEU</t>
+  </si>
+  <si>
+    <t>at grid node - Wurzburg_DEU</t>
+  </si>
+  <si>
+    <t>Friedrichshafen_DEU</t>
+  </si>
+  <si>
+    <t>at grid node - Friedrichshafen_DEU</t>
+  </si>
+  <si>
+    <t>Offenburg_DEU</t>
+  </si>
+  <si>
+    <t>at grid node - Offenburg_DEU</t>
+  </si>
+  <si>
+    <t>Jena_DEU</t>
+  </si>
+  <si>
+    <t>at grid node - Jena_DEU</t>
+  </si>
+  <si>
+    <t>Lorrach_DEU</t>
+  </si>
+  <si>
+    <t>at grid node - Lorrach_DEU</t>
+  </si>
+  <si>
+    <t>Magdeburg_DEU</t>
+  </si>
+  <si>
+    <t>at grid node - Magdeburg_DEU</t>
+  </si>
+  <si>
+    <t>Radebeul_DEU</t>
+  </si>
+  <si>
+    <t>at grid node - Radebeul_DEU</t>
+  </si>
+  <si>
+    <t>Emmendingen_DEU</t>
+  </si>
+  <si>
+    <t>at grid node - Emmendingen_DEU</t>
+  </si>
+  <si>
+    <t>Oldenburg_DEU</t>
+  </si>
+  <si>
+    <t>at grid node - Oldenburg_DEU</t>
+  </si>
+  <si>
+    <t>Saarbrucken_DEU</t>
+  </si>
+  <si>
+    <t>at grid node - Saarbrucken_DEU</t>
+  </si>
+  <si>
+    <t>Flensburg_DEU</t>
+  </si>
+  <si>
+    <t>at grid node - Flensburg_DEU</t>
+  </si>
+  <si>
+    <t>Duisburg_DEU</t>
+  </si>
+  <si>
+    <t>at grid node - Duisburg_DEU</t>
+  </si>
+  <si>
+    <t>Chemnitz_DEU</t>
+  </si>
+  <si>
+    <t>at grid node - Chemnitz_DEU</t>
+  </si>
+  <si>
     <t>Eisenhuttenstadt_DEU</t>
   </si>
   <si>
     <t>at grid node - Eisenhuttenstadt_DEU</t>
   </si>
   <si>
-    <t>Rheine_DEU</t>
-  </si>
-  <si>
-    <t>at grid node - Rheine_DEU</t>
-  </si>
-  <si>
-    <t>Cologne_DEU</t>
-  </si>
-  <si>
-    <t>at grid node - Cologne_DEU</t>
+    <t>Hamburg_DEU</t>
+  </si>
+  <si>
+    <t>at grid node - Hamburg_DEU</t>
+  </si>
+  <si>
+    <t>Bautzen_DEU</t>
+  </si>
+  <si>
+    <t>at grid node - Bautzen_DEU</t>
+  </si>
+  <si>
+    <t>Elmshorn_DEU</t>
+  </si>
+  <si>
+    <t>at grid node - Elmshorn_DEU</t>
+  </si>
+  <si>
+    <t>Gorlitz_DEU</t>
+  </si>
+  <si>
+    <t>at grid node - Gorlitz_DEU</t>
+  </si>
+  <si>
+    <t>Gustrow_DEU</t>
+  </si>
+  <si>
+    <t>at grid node - Gustrow_DEU</t>
+  </si>
+  <si>
+    <t>Weilheim_DEU</t>
+  </si>
+  <si>
+    <t>at grid node - Weilheim_DEU</t>
+  </si>
+  <si>
+    <t>Lubeck_DEU</t>
+  </si>
+  <si>
+    <t>at grid node - Lubeck_DEU</t>
+  </si>
+  <si>
+    <t>Donaueschingen_DEU</t>
+  </si>
+  <si>
+    <t>at grid node - Donaueschingen_DEU</t>
+  </si>
+  <si>
+    <t>Konz_DEU</t>
+  </si>
+  <si>
+    <t>at grid node - Konz_DEU</t>
+  </si>
+  <si>
+    <t>Kempten_DEU</t>
+  </si>
+  <si>
+    <t>at grid node - Kempten_DEU</t>
+  </si>
+  <si>
+    <t>VillingenSchwennin_DEU</t>
+  </si>
+  <si>
+    <t>at grid node - VillingenSchwennin_DEU</t>
+  </si>
+  <si>
+    <t>WaldshutTiengen_DEU</t>
+  </si>
+  <si>
+    <t>at grid node - WaldshutTiengen_DEU</t>
+  </si>
+  <si>
+    <t>FreiburgImBreisgau_DEU</t>
+  </si>
+  <si>
+    <t>at grid node - FreiburgImBreisgau_DEU</t>
   </si>
   <si>
     <t>Trier_DEU</t>
@@ -494,192 +674,12 @@
     <t>at grid node - Trier_DEU</t>
   </si>
   <si>
-    <t>Ravensburg_DEU</t>
-  </si>
-  <si>
-    <t>at grid node - Ravensburg_DEU</t>
-  </si>
-  <si>
-    <t>Emden_DEU</t>
-  </si>
-  <si>
-    <t>at grid node - Emden_DEU</t>
-  </si>
-  <si>
-    <t>Emmendingen_DEU</t>
-  </si>
-  <si>
-    <t>at grid node - Emmendingen_DEU</t>
-  </si>
-  <si>
-    <t>Wurzburg_DEU</t>
-  </si>
-  <si>
-    <t>at grid node - Wurzburg_DEU</t>
-  </si>
-  <si>
-    <t>WaldshutTiengen_DEU</t>
-  </si>
-  <si>
-    <t>at grid node - WaldshutTiengen_DEU</t>
-  </si>
-  <si>
-    <t>Offenburg_DEU</t>
-  </si>
-  <si>
-    <t>at grid node - Offenburg_DEU</t>
-  </si>
-  <si>
-    <t>Jena_DEU</t>
-  </si>
-  <si>
-    <t>at grid node - Jena_DEU</t>
-  </si>
-  <si>
     <t>RheinfeldenBaden_DEU</t>
   </si>
   <si>
     <t>at grid node - RheinfeldenBaden_DEU</t>
   </si>
   <si>
-    <t>SchwedtOder_DEU</t>
-  </si>
-  <si>
-    <t>at grid node - SchwedtOder_DEU</t>
-  </si>
-  <si>
-    <t>Magdeburg_DEU</t>
-  </si>
-  <si>
-    <t>at grid node - Magdeburg_DEU</t>
-  </si>
-  <si>
-    <t>Oldenburg_DEU</t>
-  </si>
-  <si>
-    <t>at grid node - Oldenburg_DEU</t>
-  </si>
-  <si>
-    <t>Saarbrucken_DEU</t>
-  </si>
-  <si>
-    <t>at grid node - Saarbrucken_DEU</t>
-  </si>
-  <si>
-    <t>Duisburg_DEU</t>
-  </si>
-  <si>
-    <t>at grid node - Duisburg_DEU</t>
-  </si>
-  <si>
-    <t>Ulm_DEU</t>
-  </si>
-  <si>
-    <t>at grid node - Ulm_DEU</t>
-  </si>
-  <si>
-    <t>Hamburg_DEU</t>
-  </si>
-  <si>
-    <t>at grid node - Hamburg_DEU</t>
-  </si>
-  <si>
-    <t>VillingenSchwennin_DEU</t>
-  </si>
-  <si>
-    <t>at grid node - VillingenSchwennin_DEU</t>
-  </si>
-  <si>
-    <t>Elmshorn_DEU</t>
-  </si>
-  <si>
-    <t>at grid node - Elmshorn_DEU</t>
-  </si>
-  <si>
-    <t>Friedrichshafen_DEU</t>
-  </si>
-  <si>
-    <t>at grid node - Friedrichshafen_DEU</t>
-  </si>
-  <si>
-    <t>Gustrow_DEU</t>
-  </si>
-  <si>
-    <t>at grid node - Gustrow_DEU</t>
-  </si>
-  <si>
-    <t>Bautzen_DEU</t>
-  </si>
-  <si>
-    <t>at grid node - Bautzen_DEU</t>
-  </si>
-  <si>
-    <t>Weilheim_DEU</t>
-  </si>
-  <si>
-    <t>at grid node - Weilheim_DEU</t>
-  </si>
-  <si>
-    <t>Chemnitz_DEU</t>
-  </si>
-  <si>
-    <t>at grid node - Chemnitz_DEU</t>
-  </si>
-  <si>
-    <t>Flensburg_DEU</t>
-  </si>
-  <si>
-    <t>at grid node - Flensburg_DEU</t>
-  </si>
-  <si>
-    <t>Lubeck_DEU</t>
-  </si>
-  <si>
-    <t>at grid node - Lubeck_DEU</t>
-  </si>
-  <si>
-    <t>FreiburgImBreisgau_DEU</t>
-  </si>
-  <si>
-    <t>at grid node - FreiburgImBreisgau_DEU</t>
-  </si>
-  <si>
-    <t>Konz_DEU</t>
-  </si>
-  <si>
-    <t>at grid node - Konz_DEU</t>
-  </si>
-  <si>
-    <t>Radebeul_DEU</t>
-  </si>
-  <si>
-    <t>at grid node - Radebeul_DEU</t>
-  </si>
-  <si>
-    <t>Lorrach_DEU</t>
-  </si>
-  <si>
-    <t>at grid node - Lorrach_DEU</t>
-  </si>
-  <si>
-    <t>Donaueschingen_DEU</t>
-  </si>
-  <si>
-    <t>at grid node - Donaueschingen_DEU</t>
-  </si>
-  <si>
-    <t>Kempten_DEU</t>
-  </si>
-  <si>
-    <t>at grid node - Kempten_DEU</t>
-  </si>
-  <si>
-    <t>Gorlitz_DEU</t>
-  </si>
-  <si>
-    <t>at grid node - Gorlitz_DEU</t>
-  </si>
-  <si>
     <t>CHE</t>
   </si>
   <si>
@@ -689,16 +689,94 @@
     <t>at grid node - Dietikon_CHE</t>
   </si>
   <si>
+    <t>Fully_CHE</t>
+  </si>
+  <si>
+    <t>at grid node - Fully_CHE</t>
+  </si>
+  <si>
+    <t>Thun_CHE</t>
+  </si>
+  <si>
+    <t>at grid node - Thun_CHE</t>
+  </si>
+  <si>
+    <t>Brugg_CHE</t>
+  </si>
+  <si>
+    <t>at grid node - Brugg_CHE</t>
+  </si>
+  <si>
+    <t>YverdonLesBains_CHE</t>
+  </si>
+  <si>
+    <t>at grid node - YverdonLesBains_CHE</t>
+  </si>
+  <si>
+    <t>Landquart_CHE</t>
+  </si>
+  <si>
+    <t>at grid node - Landquart_CHE</t>
+  </si>
+  <si>
+    <t>Zurich_CHE</t>
+  </si>
+  <si>
+    <t>at grid node - Zurich_CHE</t>
+  </si>
+  <si>
+    <t>BrigGlis_CHE</t>
+  </si>
+  <si>
+    <t>at grid node - BrigGlis_CHE</t>
+  </si>
+  <si>
+    <t>Chur_CHE</t>
+  </si>
+  <si>
+    <t>at grid node - Chur_CHE</t>
+  </si>
+  <si>
+    <t>Bellinzona_CHE</t>
+  </si>
+  <si>
+    <t>at grid node - Bellinzona_CHE</t>
+  </si>
+  <si>
+    <t>Davos_CHE</t>
+  </si>
+  <si>
+    <t>at grid node - Davos_CHE</t>
+  </si>
+  <si>
+    <t>Geneva_CHE</t>
+  </si>
+  <si>
+    <t>at grid node - Geneva_CHE</t>
+  </si>
+  <si>
+    <t>Winterthur_CHE</t>
+  </si>
+  <si>
+    <t>at grid node - Winterthur_CHE</t>
+  </si>
+  <si>
+    <t>Lucerne_CHE</t>
+  </si>
+  <si>
+    <t>at grid node - Lucerne_CHE</t>
+  </si>
+  <si>
     <t>Locarno_CHE</t>
   </si>
   <si>
     <t>at grid node - Locarno_CHE</t>
   </si>
   <si>
-    <t>Thun_CHE</t>
-  </si>
-  <si>
-    <t>at grid node - Thun_CHE</t>
+    <t>Bern_CHE</t>
+  </si>
+  <si>
+    <t>at grid node - Bern_CHE</t>
   </si>
   <si>
     <t>BielBienne_CHE</t>
@@ -707,94 +785,28 @@
     <t>at grid node - BielBienne_CHE</t>
   </si>
   <si>
-    <t>YverdonLesBains_CHE</t>
-  </si>
-  <si>
-    <t>at grid node - YverdonLesBains_CHE</t>
-  </si>
-  <si>
-    <t>Fully_CHE</t>
-  </si>
-  <si>
-    <t>at grid node - Fully_CHE</t>
-  </si>
-  <si>
     <t>Lugano_CHE</t>
   </si>
   <si>
     <t>at grid node - Lugano_CHE</t>
   </si>
   <si>
-    <t>Zurich_CHE</t>
-  </si>
-  <si>
-    <t>at grid node - Zurich_CHE</t>
-  </si>
-  <si>
-    <t>BrigGlis_CHE</t>
-  </si>
-  <si>
-    <t>at grid node - BrigGlis_CHE</t>
-  </si>
-  <si>
-    <t>Bellinzona_CHE</t>
-  </si>
-  <si>
-    <t>at grid node - Bellinzona_CHE</t>
-  </si>
-  <si>
     <t>Kriens_CHE</t>
   </si>
   <si>
     <t>at grid node - Kriens_CHE</t>
   </si>
   <si>
-    <t>Geneva_CHE</t>
-  </si>
-  <si>
-    <t>at grid node - Geneva_CHE</t>
-  </si>
-  <si>
-    <t>Chur_CHE</t>
-  </si>
-  <si>
-    <t>at grid node - Chur_CHE</t>
-  </si>
-  <si>
-    <t>Winterthur_CHE</t>
-  </si>
-  <si>
-    <t>at grid node - Winterthur_CHE</t>
-  </si>
-  <si>
-    <t>Davos_CHE</t>
-  </si>
-  <si>
-    <t>at grid node - Davos_CHE</t>
-  </si>
-  <si>
-    <t>Lucerne_CHE</t>
-  </si>
-  <si>
-    <t>at grid node - Lucerne_CHE</t>
-  </si>
-  <si>
-    <t>Bern_CHE</t>
-  </si>
-  <si>
-    <t>at grid node - Bern_CHE</t>
-  </si>
-  <si>
     <t>SanktGallen_CHE</t>
   </si>
   <si>
     <t>at grid node - SanktGallen_CHE</t>
   </si>
   <si>
-    <t>Landquart_CHE</t>
-  </si>
-  <si>
-    <t>at grid node - Landquart_CHE</t>
+    <t>Riehen_CHE</t>
+  </si>
+  <si>
+    <t>at grid node - Riehen_CHE</t>
   </si>
   <si>
     <t>Montreux_CHE</t>
@@ -809,18 +821,6 @@
     <t>at grid node - Aarau_CHE</t>
   </si>
   <si>
-    <t>Riehen_CHE</t>
-  </si>
-  <si>
-    <t>at grid node - Riehen_CHE</t>
-  </si>
-  <si>
-    <t>Brugg_CHE</t>
-  </si>
-  <si>
-    <t>at grid node - Brugg_CHE</t>
-  </si>
-  <si>
     <t>ITA</t>
   </si>
   <si>
@@ -836,28 +836,106 @@
     <t>at grid node - Pescara_ITA</t>
   </si>
   <si>
+    <t>Civitavecchia_ITA</t>
+  </si>
+  <si>
+    <t>at grid node - Civitavecchia_ITA</t>
+  </si>
+  <si>
+    <t>Pordenone_ITA</t>
+  </si>
+  <si>
+    <t>at grid node - Pordenone_ITA</t>
+  </si>
+  <si>
+    <t>Brescia_ITA</t>
+  </si>
+  <si>
+    <t>at grid node - Brescia_ITA</t>
+  </si>
+  <si>
+    <t>Lecce_ITA</t>
+  </si>
+  <si>
+    <t>at grid node - Lecce_ITA</t>
+  </si>
+  <si>
+    <t>Latina_ITA</t>
+  </si>
+  <si>
+    <t>at grid node - Latina_ITA</t>
+  </si>
+  <si>
+    <t>Como_ITA</t>
+  </si>
+  <si>
+    <t>at grid node - Como_ITA</t>
+  </si>
+  <si>
+    <t>Aosta_ITA</t>
+  </si>
+  <si>
+    <t>at grid node - Aosta_ITA</t>
+  </si>
+  <si>
+    <t>Milan_ITA</t>
+  </si>
+  <si>
+    <t>at grid node - Milan_ITA</t>
+  </si>
+  <si>
+    <t>Piombino_ITA</t>
+  </si>
+  <si>
+    <t>at grid node - Piombino_ITA</t>
+  </si>
+  <si>
+    <t>Verbania_ITA</t>
+  </si>
+  <si>
+    <t>at grid node - Verbania_ITA</t>
+  </si>
+  <si>
+    <t>Alghero_ITA</t>
+  </si>
+  <si>
+    <t>at grid node - Alghero_ITA</t>
+  </si>
+  <si>
+    <t>Calimera_ITA</t>
+  </si>
+  <si>
+    <t>at grid node - Calimera_ITA</t>
+  </si>
+  <si>
+    <t>Trento_ITA</t>
+  </si>
+  <si>
+    <t>at grid node - Trento_ITA</t>
+  </si>
+  <si>
     <t>Sassari_ITA</t>
   </si>
   <si>
     <t>at grid node - Sassari_ITA</t>
   </si>
   <si>
-    <t>Pordenone_ITA</t>
-  </si>
-  <si>
-    <t>at grid node - Pordenone_ITA</t>
-  </si>
-  <si>
-    <t>Brescia_ITA</t>
-  </si>
-  <si>
-    <t>at grid node - Brescia_ITA</t>
-  </si>
-  <si>
-    <t>Latina_ITA</t>
-  </si>
-  <si>
-    <t>at grid node - Latina_ITA</t>
+    <t>Lana_ITA</t>
+  </si>
+  <si>
+    <t>at grid node - Lana_ITA</t>
+  </si>
+  <si>
+    <t>Palermo_ITA</t>
+  </si>
+  <si>
+    <t>at grid node - Palermo_ITA</t>
+  </si>
+  <si>
+    <t>Trieste_ITA</t>
+  </si>
+  <si>
+    <t>at grid node - Trieste_ITA</t>
   </si>
   <si>
     <t>Domodossola_ITA</t>
@@ -866,28 +944,10 @@
     <t>at grid node - Domodossola_ITA</t>
   </si>
   <si>
-    <t>Aosta_ITA</t>
-  </si>
-  <si>
-    <t>at grid node - Aosta_ITA</t>
-  </si>
-  <si>
-    <t>Milan_ITA</t>
-  </si>
-  <si>
-    <t>at grid node - Milan_ITA</t>
-  </si>
-  <si>
-    <t>Civitavecchia_ITA</t>
-  </si>
-  <si>
-    <t>at grid node - Civitavecchia_ITA</t>
-  </si>
-  <si>
-    <t>Lecce_ITA</t>
-  </si>
-  <si>
-    <t>at grid node - Lecce_ITA</t>
+    <t>Gorizia_ITA</t>
+  </si>
+  <si>
+    <t>at grid node - Gorizia_ITA</t>
   </si>
   <si>
     <t>Tirano_ITA</t>
@@ -896,70 +956,16 @@
     <t>at grid node - Tirano_ITA</t>
   </si>
   <si>
-    <t>Piombino_ITA</t>
-  </si>
-  <si>
-    <t>at grid node - Piombino_ITA</t>
-  </si>
-  <si>
-    <t>Verbania_ITA</t>
-  </si>
-  <si>
-    <t>at grid node - Verbania_ITA</t>
-  </si>
-  <si>
-    <t>Gorizia_ITA</t>
-  </si>
-  <si>
-    <t>at grid node - Gorizia_ITA</t>
-  </si>
-  <si>
-    <t>Trento_ITA</t>
-  </si>
-  <si>
-    <t>at grid node - Trento_ITA</t>
-  </si>
-  <si>
     <t>SanRemo_ITA</t>
   </si>
   <si>
     <t>at grid node - SanRemo_ITA</t>
   </si>
   <si>
-    <t>Alghero_ITA</t>
-  </si>
-  <si>
-    <t>at grid node - Alghero_ITA</t>
-  </si>
-  <si>
-    <t>Calimera_ITA</t>
-  </si>
-  <si>
-    <t>at grid node - Calimera_ITA</t>
-  </si>
-  <si>
-    <t>Trieste_ITA</t>
-  </si>
-  <si>
-    <t>at grid node - Trieste_ITA</t>
-  </si>
-  <si>
-    <t>Como_ITA</t>
-  </si>
-  <si>
-    <t>at grid node - Como_ITA</t>
-  </si>
-  <si>
-    <t>Lana_ITA</t>
-  </si>
-  <si>
-    <t>at grid node - Lana_ITA</t>
-  </si>
-  <si>
-    <t>Palermo_ITA</t>
-  </si>
-  <si>
-    <t>at grid node - Palermo_ITA</t>
+    <t>Morbegno_ITA</t>
+  </si>
+  <si>
+    <t>at grid node - Morbegno_ITA</t>
   </si>
   <si>
     <t>Pinerolo_ITA</t>
@@ -968,12 +974,6 @@
     <t>at grid node - Pinerolo_ITA</t>
   </si>
   <si>
-    <t>Morbegno_ITA</t>
-  </si>
-  <si>
-    <t>at grid node - Morbegno_ITA</t>
-  </si>
-  <si>
     <t>ESP</t>
   </si>
   <si>
@@ -989,96 +989,96 @@
     <t>at grid node - Donostia_ESP</t>
   </si>
   <si>
+    <t>NavalmoralDeLaMata_ESP</t>
+  </si>
+  <si>
+    <t>at grid node - NavalmoralDeLaMata_ESP</t>
+  </si>
+  <si>
+    <t>ACoruna_ESP</t>
+  </si>
+  <si>
+    <t>at grid node - ACoruna_ESP</t>
+  </si>
+  <si>
+    <t>Valladolid_ESP</t>
+  </si>
+  <si>
+    <t>at grid node - Valladolid_ESP</t>
+  </si>
+  <si>
+    <t>Granollers_ESP</t>
+  </si>
+  <si>
+    <t>at grid node - Granollers_ESP</t>
+  </si>
+  <si>
+    <t>Palma_ESP</t>
+  </si>
+  <si>
+    <t>at grid node - Palma_ESP</t>
+  </si>
+  <si>
+    <t>Lepe_ESP</t>
+  </si>
+  <si>
+    <t>at grid node - Lepe_ESP</t>
+  </si>
+  <si>
+    <t>Barcelona_ESP</t>
+  </si>
+  <si>
+    <t>at grid node - Barcelona_ESP</t>
+  </si>
+  <si>
+    <t>Zafra_ESP</t>
+  </si>
+  <si>
+    <t>at grid node - Zafra_ESP</t>
+  </si>
+  <si>
+    <t>CastellonDeLaPlana_ESP</t>
+  </si>
+  <si>
+    <t>at grid node - CastellonDeLaPlana_ESP</t>
+  </si>
+  <si>
+    <t>Algeciras_ESP</t>
+  </si>
+  <si>
+    <t>at grid node - Algeciras_ESP</t>
+  </si>
+  <si>
+    <t>Jaca_ESP</t>
+  </si>
+  <si>
+    <t>at grid node - Jaca_ESP</t>
+  </si>
+  <si>
+    <t>Coria_ESP</t>
+  </si>
+  <si>
+    <t>at grid node - Coria_ESP</t>
+  </si>
+  <si>
+    <t>Zamora_ESP</t>
+  </si>
+  <si>
+    <t>at grid node - Zamora_ESP</t>
+  </si>
+  <si>
+    <t>SalvatierraDeMino_ESP</t>
+  </si>
+  <si>
+    <t>at grid node - SalvatierraDeMino_ESP</t>
+  </si>
+  <si>
     <t>Girona_ESP</t>
   </si>
   <si>
     <t>at grid node - Girona_ESP</t>
   </si>
   <si>
-    <t>ACoruna_ESP</t>
-  </si>
-  <si>
-    <t>at grid node - ACoruna_ESP</t>
-  </si>
-  <si>
-    <t>Valladolid_ESP</t>
-  </si>
-  <si>
-    <t>at grid node - Valladolid_ESP</t>
-  </si>
-  <si>
-    <t>NavalmoralDeLaMata_ESP</t>
-  </si>
-  <si>
-    <t>at grid node - NavalmoralDeLaMata_ESP</t>
-  </si>
-  <si>
-    <t>Palma_ESP</t>
-  </si>
-  <si>
-    <t>at grid node - Palma_ESP</t>
-  </si>
-  <si>
-    <t>Zafra_ESP</t>
-  </si>
-  <si>
-    <t>at grid node - Zafra_ESP</t>
-  </si>
-  <si>
-    <t>Lepe_ESP</t>
-  </si>
-  <si>
-    <t>at grid node - Lepe_ESP</t>
-  </si>
-  <si>
-    <t>Barcelona_ESP</t>
-  </si>
-  <si>
-    <t>at grid node - Barcelona_ESP</t>
-  </si>
-  <si>
-    <t>Algeciras_ESP</t>
-  </si>
-  <si>
-    <t>at grid node - Algeciras_ESP</t>
-  </si>
-  <si>
-    <t>CastellonDeLaPlana_ESP</t>
-  </si>
-  <si>
-    <t>at grid node - CastellonDeLaPlana_ESP</t>
-  </si>
-  <si>
-    <t>Jaca_ESP</t>
-  </si>
-  <si>
-    <t>at grid node - Jaca_ESP</t>
-  </si>
-  <si>
-    <t>Zamora_ESP</t>
-  </si>
-  <si>
-    <t>at grid node - Zamora_ESP</t>
-  </si>
-  <si>
-    <t>Granollers_ESP</t>
-  </si>
-  <si>
-    <t>at grid node - Granollers_ESP</t>
-  </si>
-  <si>
-    <t>Coria_ESP</t>
-  </si>
-  <si>
-    <t>at grid node - Coria_ESP</t>
-  </si>
-  <si>
-    <t>SalvatierraDeMino_ESP</t>
-  </si>
-  <si>
-    <t>at grid node - SalvatierraDeMino_ESP</t>
-  </si>
-  <si>
     <t>NLD</t>
   </si>
   <si>
@@ -1094,6 +1094,12 @@
     <t>at grid node - Amsterdam_NLD</t>
   </si>
   <si>
+    <t>Nijmegen_NLD</t>
+  </si>
+  <si>
+    <t>at grid node - Nijmegen_NLD</t>
+  </si>
+  <si>
     <t>Tilburg_NLD</t>
   </si>
   <si>
@@ -1106,12 +1112,6 @@
     <t>at grid node - Maastricht_NLD</t>
   </si>
   <si>
-    <t>Nijmegen_NLD</t>
-  </si>
-  <si>
-    <t>at grid node - Nijmegen_NLD</t>
-  </si>
-  <si>
     <t>Leeuwarden_NLD</t>
   </si>
   <si>
@@ -1124,28 +1124,28 @@
     <t>at grid node - Hoogezand_NLD</t>
   </si>
   <si>
+    <t>Veendam_NLD</t>
+  </si>
+  <si>
+    <t>at grid node - Veendam_NLD</t>
+  </si>
+  <si>
+    <t>Enschede_NLD</t>
+  </si>
+  <si>
+    <t>at grid node - Enschede_NLD</t>
+  </si>
+  <si>
+    <t>Rotterdam_NLD</t>
+  </si>
+  <si>
+    <t>at grid node - Rotterdam_NLD</t>
+  </si>
+  <si>
     <t>Eindhoven_NLD</t>
   </si>
   <si>
     <t>at grid node - Eindhoven_NLD</t>
-  </si>
-  <si>
-    <t>Veendam_NLD</t>
-  </si>
-  <si>
-    <t>at grid node - Veendam_NLD</t>
-  </si>
-  <si>
-    <t>Enschede_NLD</t>
-  </si>
-  <si>
-    <t>at grid node - Enschede_NLD</t>
-  </si>
-  <si>
-    <t>Rotterdam_NLD</t>
-  </si>
-  <si>
-    <t>at grid node - Rotterdam_NLD</t>
   </si>
   <si>
     <t>Apeldoorn_NLD</t>
@@ -1728,7 +1728,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AE38895-A278-4E93-A65F-C4146FDB7DDF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F16B6F0-E12C-4201-91B0-E9BC8D46D6B2}">
   <dimension ref="B9:Y44"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2088,10 +2088,10 @@
         <v>8</v>
       </c>
       <c r="M15" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="N15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="O15" t="s">
         <v>17</v>
@@ -2150,10 +2150,10 @@
         <v>8</v>
       </c>
       <c r="M16" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="N16" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="O16" t="s">
         <v>17</v>
@@ -2188,10 +2188,10 @@
         <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E17" t="s">
         <v>11</v>
@@ -2212,10 +2212,10 @@
         <v>8</v>
       </c>
       <c r="M17" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="N17" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="O17" t="s">
         <v>17</v>
@@ -2224,10 +2224,10 @@
         <v>8</v>
       </c>
       <c r="R17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="S17" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="T17" t="s">
         <v>18</v>
@@ -2236,10 +2236,10 @@
         <v>8</v>
       </c>
       <c r="W17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="X17" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Y17" t="s">
         <v>19</v>
@@ -2274,23 +2274,23 @@
         <v>8</v>
       </c>
       <c r="M18" t="s">
+        <v>46</v>
+      </c>
+      <c r="N18" t="s">
+        <v>47</v>
+      </c>
+      <c r="O18" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" t="s">
         <v>48</v>
       </c>
-      <c r="N18" t="s">
+      <c r="S18" t="s">
         <v>49</v>
       </c>
-      <c r="O18" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>8</v>
-      </c>
-      <c r="R18" t="s">
-        <v>50</v>
-      </c>
-      <c r="S18" t="s">
-        <v>51</v>
-      </c>
       <c r="T18" t="s">
         <v>18</v>
       </c>
@@ -2298,10 +2298,10 @@
         <v>8</v>
       </c>
       <c r="W18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="X18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Y18" t="s">
         <v>19</v>
@@ -2312,10 +2312,10 @@
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D19" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E19" t="s">
         <v>11</v>
@@ -2336,10 +2336,10 @@
         <v>8</v>
       </c>
       <c r="M19" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="N19" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="O19" t="s">
         <v>17</v>
@@ -2386,10 +2386,10 @@
         <v>8</v>
       </c>
       <c r="H20" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J20" t="s">
         <v>14</v>
@@ -2398,10 +2398,10 @@
         <v>8</v>
       </c>
       <c r="M20" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="N20" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="O20" t="s">
         <v>17</v>
@@ -2410,10 +2410,10 @@
         <v>8</v>
       </c>
       <c r="R20" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="S20" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="T20" t="s">
         <v>18</v>
@@ -2422,10 +2422,10 @@
         <v>8</v>
       </c>
       <c r="W20" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="X20" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="Y20" t="s">
         <v>19</v>
@@ -2436,10 +2436,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="D21" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="E21" t="s">
         <v>11</v>
@@ -2448,10 +2448,10 @@
         <v>8</v>
       </c>
       <c r="H21" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I21" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J21" t="s">
         <v>14</v>
@@ -2460,10 +2460,10 @@
         <v>8</v>
       </c>
       <c r="M21" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N21" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="O21" t="s">
         <v>17</v>
@@ -2498,10 +2498,10 @@
         <v>8</v>
       </c>
       <c r="C22" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D22" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E22" t="s">
         <v>11</v>
@@ -2510,10 +2510,10 @@
         <v>8</v>
       </c>
       <c r="H22" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="I22" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="J22" t="s">
         <v>14</v>
@@ -2522,10 +2522,10 @@
         <v>8</v>
       </c>
       <c r="M22" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="N22" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="O22" t="s">
         <v>17</v>
@@ -2534,10 +2534,10 @@
         <v>8</v>
       </c>
       <c r="R22" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="S22" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="T22" t="s">
         <v>18</v>
@@ -2546,10 +2546,10 @@
         <v>8</v>
       </c>
       <c r="W22" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="X22" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="Y22" t="s">
         <v>19</v>
@@ -2560,10 +2560,10 @@
         <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="D23" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="E23" t="s">
         <v>11</v>
@@ -2572,10 +2572,10 @@
         <v>8</v>
       </c>
       <c r="H23" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I23" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J23" t="s">
         <v>14</v>
@@ -2584,10 +2584,10 @@
         <v>8</v>
       </c>
       <c r="M23" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="N23" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="O23" t="s">
         <v>17</v>
@@ -2596,10 +2596,10 @@
         <v>8</v>
       </c>
       <c r="R23" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S23" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T23" t="s">
         <v>18</v>
@@ -2608,10 +2608,10 @@
         <v>8</v>
       </c>
       <c r="W23" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="X23" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="Y23" t="s">
         <v>19</v>
@@ -2622,10 +2622,10 @@
         <v>8</v>
       </c>
       <c r="C24" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D24" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E24" t="s">
         <v>11</v>
@@ -2634,10 +2634,10 @@
         <v>8</v>
       </c>
       <c r="H24" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="I24" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="J24" t="s">
         <v>14</v>
@@ -2646,10 +2646,10 @@
         <v>8</v>
       </c>
       <c r="M24" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="N24" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="O24" t="s">
         <v>17</v>
@@ -2684,10 +2684,10 @@
         <v>8</v>
       </c>
       <c r="C25" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="D25" t="s">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="E25" t="s">
         <v>11</v>
@@ -2696,10 +2696,10 @@
         <v>8</v>
       </c>
       <c r="H25" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="I25" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J25" t="s">
         <v>14</v>
@@ -2720,10 +2720,10 @@
         <v>8</v>
       </c>
       <c r="R25" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="S25" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="T25" t="s">
         <v>18</v>
@@ -2732,10 +2732,10 @@
         <v>8</v>
       </c>
       <c r="W25" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="X25" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="Y25" t="s">
         <v>19</v>
@@ -2746,10 +2746,10 @@
         <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="D26" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="E26" t="s">
         <v>11</v>
@@ -2758,10 +2758,10 @@
         <v>8</v>
       </c>
       <c r="H26" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I26" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J26" t="s">
         <v>14</v>
@@ -2770,10 +2770,10 @@
         <v>8</v>
       </c>
       <c r="M26" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="N26" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="O26" t="s">
         <v>17</v>
@@ -2782,10 +2782,10 @@
         <v>8</v>
       </c>
       <c r="R26" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="S26" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="T26" t="s">
         <v>18</v>
@@ -2794,10 +2794,10 @@
         <v>8</v>
       </c>
       <c r="W26" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="X26" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="Y26" t="s">
         <v>19</v>
@@ -2808,10 +2808,10 @@
         <v>8</v>
       </c>
       <c r="C27" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D27" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E27" t="s">
         <v>11</v>
@@ -2820,10 +2820,10 @@
         <v>8</v>
       </c>
       <c r="H27" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="I27" t="s">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="J27" t="s">
         <v>14</v>
@@ -2832,10 +2832,10 @@
         <v>8</v>
       </c>
       <c r="M27" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="N27" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="O27" t="s">
         <v>17</v>
@@ -2844,10 +2844,10 @@
         <v>8</v>
       </c>
       <c r="R27" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="S27" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="T27" t="s">
         <v>18</v>
@@ -2856,10 +2856,10 @@
         <v>8</v>
       </c>
       <c r="W27" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="X27" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="Y27" t="s">
         <v>19</v>
@@ -2882,10 +2882,10 @@
         <v>8</v>
       </c>
       <c r="H28" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="I28" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="J28" t="s">
         <v>14</v>
@@ -2894,10 +2894,10 @@
         <v>8</v>
       </c>
       <c r="M28" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="N28" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="O28" t="s">
         <v>17</v>
@@ -2906,10 +2906,10 @@
         <v>8</v>
       </c>
       <c r="R28" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="S28" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="T28" t="s">
         <v>18</v>
@@ -2918,10 +2918,10 @@
         <v>8</v>
       </c>
       <c r="W28" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="X28" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="Y28" t="s">
         <v>19</v>
@@ -2932,10 +2932,10 @@
         <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="D29" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="E29" t="s">
         <v>11</v>
@@ -2956,10 +2956,10 @@
         <v>8</v>
       </c>
       <c r="M29" t="s">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="N29" t="s">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="O29" t="s">
         <v>17</v>
@@ -2968,10 +2968,10 @@
         <v>8</v>
       </c>
       <c r="R29" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="S29" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="T29" t="s">
         <v>18</v>
@@ -2980,10 +2980,10 @@
         <v>8</v>
       </c>
       <c r="W29" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="X29" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="Y29" t="s">
         <v>19</v>
@@ -2994,10 +2994,10 @@
         <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="D30" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="E30" t="s">
         <v>11</v>
@@ -3006,10 +3006,10 @@
         <v>8</v>
       </c>
       <c r="H30" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="I30" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="J30" t="s">
         <v>14</v>
@@ -3018,10 +3018,10 @@
         <v>8</v>
       </c>
       <c r="M30" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="N30" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="O30" t="s">
         <v>17</v>
@@ -3056,10 +3056,10 @@
         <v>8</v>
       </c>
       <c r="C31" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="D31" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="E31" t="s">
         <v>11</v>
@@ -3068,10 +3068,10 @@
         <v>8</v>
       </c>
       <c r="H31" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="I31" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="J31" t="s">
         <v>14</v>
@@ -3080,23 +3080,23 @@
         <v>8</v>
       </c>
       <c r="M31" t="s">
+        <v>74</v>
+      </c>
+      <c r="N31" t="s">
+        <v>75</v>
+      </c>
+      <c r="O31" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>8</v>
+      </c>
+      <c r="R31" t="s">
         <v>72</v>
       </c>
-      <c r="N31" t="s">
+      <c r="S31" t="s">
         <v>73</v>
       </c>
-      <c r="O31" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>8</v>
-      </c>
-      <c r="R31" t="s">
-        <v>36</v>
-      </c>
-      <c r="S31" t="s">
-        <v>37</v>
-      </c>
       <c r="T31" t="s">
         <v>18</v>
       </c>
@@ -3104,10 +3104,10 @@
         <v>8</v>
       </c>
       <c r="W31" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="X31" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="Y31" t="s">
         <v>19</v>
@@ -3130,10 +3130,10 @@
         <v>8</v>
       </c>
       <c r="H32" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="I32" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="J32" t="s">
         <v>14</v>
@@ -3142,10 +3142,10 @@
         <v>8</v>
       </c>
       <c r="M32" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="N32" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="O32" t="s">
         <v>17</v>
@@ -3156,10 +3156,10 @@
         <v>8</v>
       </c>
       <c r="H33" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I33" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J33" t="s">
         <v>14</v>
@@ -3168,10 +3168,10 @@
         <v>8</v>
       </c>
       <c r="M33" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="N33" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="O33" t="s">
         <v>17</v>
@@ -3182,10 +3182,10 @@
         <v>8</v>
       </c>
       <c r="H34" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="I34" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="J34" t="s">
         <v>14</v>
@@ -3194,10 +3194,10 @@
         <v>8</v>
       </c>
       <c r="M34" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="N34" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="O34" t="s">
         <v>17</v>
@@ -3208,10 +3208,10 @@
         <v>8</v>
       </c>
       <c r="H35" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I35" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J35" t="s">
         <v>14</v>
@@ -3220,10 +3220,10 @@
         <v>8</v>
       </c>
       <c r="M35" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="N35" t="s">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="O35" t="s">
         <v>17</v>
@@ -3234,10 +3234,10 @@
         <v>8</v>
       </c>
       <c r="H36" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="I36" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="J36" t="s">
         <v>14</v>
@@ -3246,10 +3246,10 @@
         <v>8</v>
       </c>
       <c r="M36" t="s">
-        <v>78</v>
+        <v>9</v>
       </c>
       <c r="N36" t="s">
-        <v>79</v>
+        <v>10</v>
       </c>
       <c r="O36" t="s">
         <v>17</v>
@@ -3260,10 +3260,10 @@
         <v>8</v>
       </c>
       <c r="H37" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="I37" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="J37" t="s">
         <v>14</v>
@@ -3272,10 +3272,10 @@
         <v>8</v>
       </c>
       <c r="M37" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="N37" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="O37" t="s">
         <v>17</v>
@@ -3286,10 +3286,10 @@
         <v>8</v>
       </c>
       <c r="H38" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I38" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J38" t="s">
         <v>14</v>
@@ -3298,10 +3298,10 @@
         <v>8</v>
       </c>
       <c r="M38" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N38" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="O38" t="s">
         <v>17</v>
@@ -3324,10 +3324,10 @@
         <v>8</v>
       </c>
       <c r="M39" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="N39" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="O39" t="s">
         <v>17</v>
@@ -3338,10 +3338,10 @@
         <v>8</v>
       </c>
       <c r="H40" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="I40" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="J40" t="s">
         <v>14</v>
@@ -3350,10 +3350,10 @@
         <v>8</v>
       </c>
       <c r="M40" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="N40" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="O40" t="s">
         <v>17</v>
@@ -3364,10 +3364,10 @@
         <v>8</v>
       </c>
       <c r="H41" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I41" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J41" t="s">
         <v>14</v>
@@ -3376,10 +3376,10 @@
         <v>8</v>
       </c>
       <c r="M41" t="s">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="N41" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="O41" t="s">
         <v>17</v>
@@ -3402,10 +3402,10 @@
         <v>8</v>
       </c>
       <c r="M42" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="N42" t="s">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="O42" t="s">
         <v>17</v>
@@ -3416,10 +3416,10 @@
         <v>8</v>
       </c>
       <c r="H43" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="I43" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="J43" t="s">
         <v>14</v>
@@ -3428,10 +3428,10 @@
         <v>8</v>
       </c>
       <c r="M43" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="N43" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="O43" t="s">
         <v>17</v>
@@ -3442,10 +3442,10 @@
         <v>8</v>
       </c>
       <c r="M44" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="N44" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="O44" t="s">
         <v>17</v>
@@ -3457,7 +3457,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{844291C7-9F5E-4EF3-AB96-9F565197CCE0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA51C0E1-F82D-49AF-A662-9135EA48EC5C}">
   <dimension ref="C4:X58"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -4362,7 +4362,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{705F9F4C-68B9-4C19-878E-28DE9A18BFE6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86241E67-6DF5-427D-A6E7-F61FE7A0981D}">
   <dimension ref="B9:Y25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4574,10 +4574,10 @@
         <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D13" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
@@ -4598,10 +4598,10 @@
         <v>82</v>
       </c>
       <c r="M13" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="N13" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="O13" t="s">
         <v>17</v>
@@ -4610,10 +4610,10 @@
         <v>82</v>
       </c>
       <c r="R13" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="S13" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="T13" t="s">
         <v>18</v>
@@ -4622,10 +4622,10 @@
         <v>82</v>
       </c>
       <c r="W13" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="X13" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="Y13" t="s">
         <v>19</v>
@@ -4648,10 +4648,10 @@
         <v>82</v>
       </c>
       <c r="H14" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="I14" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="J14" t="s">
         <v>14</v>
@@ -4660,10 +4660,10 @@
         <v>82</v>
       </c>
       <c r="M14" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="N14" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O14" t="s">
         <v>17</v>
@@ -4698,10 +4698,10 @@
         <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D15" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="E15" t="s">
         <v>11</v>
@@ -4722,10 +4722,10 @@
         <v>82</v>
       </c>
       <c r="M15" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N15" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O15" t="s">
         <v>17</v>
@@ -4734,10 +4734,10 @@
         <v>82</v>
       </c>
       <c r="R15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="S15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="T15" t="s">
         <v>18</v>
@@ -4746,10 +4746,10 @@
         <v>82</v>
       </c>
       <c r="W15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="X15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="Y15" t="s">
         <v>19</v>
@@ -4760,10 +4760,10 @@
         <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D16" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E16" t="s">
         <v>11</v>
@@ -4772,10 +4772,10 @@
         <v>82</v>
       </c>
       <c r="H16" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="I16" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="J16" t="s">
         <v>14</v>
@@ -4784,10 +4784,10 @@
         <v>82</v>
       </c>
       <c r="M16" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N16" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="O16" t="s">
         <v>17</v>
@@ -4822,10 +4822,10 @@
         <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D17" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E17" t="s">
         <v>11</v>
@@ -4846,10 +4846,10 @@
         <v>82</v>
       </c>
       <c r="M17" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N17" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="O17" t="s">
         <v>17</v>
@@ -4858,10 +4858,10 @@
         <v>82</v>
       </c>
       <c r="R17" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="S17" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="T17" t="s">
         <v>18</v>
@@ -4870,10 +4870,10 @@
         <v>82</v>
       </c>
       <c r="W17" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="X17" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="Y17" t="s">
         <v>19</v>
@@ -4896,10 +4896,10 @@
         <v>82</v>
       </c>
       <c r="H18" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I18" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="J18" t="s">
         <v>14</v>
@@ -4908,10 +4908,10 @@
         <v>82</v>
       </c>
       <c r="M18" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="N18" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="O18" t="s">
         <v>17</v>
@@ -4958,10 +4958,10 @@
         <v>82</v>
       </c>
       <c r="H19" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I19" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="J19" t="s">
         <v>14</v>
@@ -4970,10 +4970,10 @@
         <v>82</v>
       </c>
       <c r="M19" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="N19" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="O19" t="s">
         <v>17</v>
@@ -5008,10 +5008,10 @@
         <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D20" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E20" t="s">
         <v>11</v>
@@ -5020,10 +5020,10 @@
         <v>82</v>
       </c>
       <c r="H20" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I20" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J20" t="s">
         <v>14</v>
@@ -5032,10 +5032,10 @@
         <v>82</v>
       </c>
       <c r="M20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="N20" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="O20" t="s">
         <v>17</v>
@@ -5044,10 +5044,10 @@
         <v>82</v>
       </c>
       <c r="R20" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="S20" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="T20" t="s">
         <v>18</v>
@@ -5056,10 +5056,10 @@
         <v>82</v>
       </c>
       <c r="W20" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="X20" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="Y20" t="s">
         <v>19</v>
@@ -5070,10 +5070,10 @@
         <v>82</v>
       </c>
       <c r="H21" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="I21" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="J21" t="s">
         <v>14</v>
@@ -5094,10 +5094,10 @@
         <v>82</v>
       </c>
       <c r="R21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="S21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="T21" t="s">
         <v>18</v>
@@ -5106,10 +5106,10 @@
         <v>82</v>
       </c>
       <c r="W21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="X21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Y21" t="s">
         <v>19</v>
@@ -5132,10 +5132,10 @@
         <v>82</v>
       </c>
       <c r="M22" t="s">
-        <v>111</v>
+        <v>85</v>
       </c>
       <c r="N22" t="s">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="O22" t="s">
         <v>17</v>
@@ -5144,10 +5144,10 @@
         <v>82</v>
       </c>
       <c r="R22" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="S22" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="T22" t="s">
         <v>18</v>
@@ -5156,10 +5156,10 @@
         <v>82</v>
       </c>
       <c r="W22" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="X22" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="Y22" t="s">
         <v>19</v>
@@ -5182,10 +5182,10 @@
         <v>82</v>
       </c>
       <c r="M23" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="N23" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="O23" t="s">
         <v>17</v>
@@ -5208,10 +5208,10 @@
         <v>82</v>
       </c>
       <c r="M24" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="N24" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="O24" t="s">
         <v>17</v>
@@ -5222,10 +5222,10 @@
         <v>82</v>
       </c>
       <c r="H25" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="I25" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="J25" t="s">
         <v>14</v>
@@ -5234,10 +5234,10 @@
         <v>82</v>
       </c>
       <c r="M25" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="N25" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="O25" t="s">
         <v>17</v>
@@ -5249,7 +5249,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE2FBD03-69E5-48BD-9C6A-F85D96956110}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6846A998-B057-46FE-B989-B28F9FCE3C62}">
   <dimension ref="B9:Y21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5485,10 +5485,10 @@
         <v>113</v>
       </c>
       <c r="M13" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="N13" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="O13" t="s">
         <v>17</v>
@@ -5535,10 +5535,10 @@
         <v>113</v>
       </c>
       <c r="H14" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="I14" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="J14" t="s">
         <v>14</v>
@@ -5547,10 +5547,10 @@
         <v>113</v>
       </c>
       <c r="M14" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="N14" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="O14" t="s">
         <v>17</v>
@@ -5609,10 +5609,10 @@
         <v>113</v>
       </c>
       <c r="M15" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="N15" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="O15" t="s">
         <v>17</v>
@@ -5621,10 +5621,10 @@
         <v>113</v>
       </c>
       <c r="R15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="S15" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="T15" t="s">
         <v>18</v>
@@ -5633,10 +5633,10 @@
         <v>113</v>
       </c>
       <c r="W15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="X15" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="Y15" t="s">
         <v>19</v>
@@ -5647,10 +5647,10 @@
         <v>113</v>
       </c>
       <c r="C16" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D16" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E16" t="s">
         <v>11</v>
@@ -5671,10 +5671,10 @@
         <v>113</v>
       </c>
       <c r="M16" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="N16" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="O16" t="s">
         <v>17</v>
@@ -5709,10 +5709,10 @@
         <v>113</v>
       </c>
       <c r="H17" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I17" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="J17" t="s">
         <v>14</v>
@@ -5721,10 +5721,10 @@
         <v>113</v>
       </c>
       <c r="M17" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="N17" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="O17" t="s">
         <v>17</v>
@@ -5735,10 +5735,10 @@
         <v>113</v>
       </c>
       <c r="M18" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="N18" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="O18" t="s">
         <v>17</v>
@@ -5749,10 +5749,10 @@
         <v>113</v>
       </c>
       <c r="M19" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="N19" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="O19" t="s">
         <v>17</v>
@@ -5763,10 +5763,10 @@
         <v>113</v>
       </c>
       <c r="M20" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="N20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="O20" t="s">
         <v>17</v>
@@ -5777,10 +5777,10 @@
         <v>113</v>
       </c>
       <c r="M21" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="N21" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="O21" t="s">
         <v>17</v>
@@ -5792,7 +5792,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBC9C38A-0D68-4FC5-89F0-29AEE099FA0E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5A18397-8B3A-4818-98E5-7EFC4B398412}">
   <dimension ref="B9:Y47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5966,10 +5966,10 @@
         <v>136</v>
       </c>
       <c r="M12" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="O12" t="s">
         <v>17</v>
@@ -6004,10 +6004,10 @@
         <v>136</v>
       </c>
       <c r="C13" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D13" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
@@ -6016,23 +6016,23 @@
         <v>136</v>
       </c>
       <c r="H13" t="s">
+        <v>149</v>
+      </c>
+      <c r="I13" t="s">
+        <v>150</v>
+      </c>
+      <c r="J13" t="s">
+        <v>14</v>
+      </c>
+      <c r="L13" t="s">
+        <v>136</v>
+      </c>
+      <c r="M13" t="s">
         <v>151</v>
       </c>
-      <c r="I13" t="s">
+      <c r="N13" t="s">
         <v>152</v>
       </c>
-      <c r="J13" t="s">
-        <v>14</v>
-      </c>
-      <c r="L13" t="s">
-        <v>136</v>
-      </c>
-      <c r="M13" t="s">
-        <v>153</v>
-      </c>
-      <c r="N13" t="s">
-        <v>154</v>
-      </c>
       <c r="O13" t="s">
         <v>17</v>
       </c>
@@ -6040,10 +6040,10 @@
         <v>136</v>
       </c>
       <c r="R13" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="S13" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="T13" t="s">
         <v>18</v>
@@ -6052,10 +6052,10 @@
         <v>136</v>
       </c>
       <c r="W13" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="X13" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="Y13" t="s">
         <v>19</v>
@@ -6066,10 +6066,10 @@
         <v>136</v>
       </c>
       <c r="C14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D14" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E14" t="s">
         <v>11</v>
@@ -6078,35 +6078,35 @@
         <v>136</v>
       </c>
       <c r="H14" t="s">
+        <v>153</v>
+      </c>
+      <c r="I14" t="s">
+        <v>154</v>
+      </c>
+      <c r="J14" t="s">
+        <v>14</v>
+      </c>
+      <c r="L14" t="s">
+        <v>136</v>
+      </c>
+      <c r="M14" t="s">
         <v>155</v>
       </c>
-      <c r="I14" t="s">
+      <c r="N14" t="s">
         <v>156</v>
       </c>
-      <c r="J14" t="s">
-        <v>14</v>
-      </c>
-      <c r="L14" t="s">
-        <v>136</v>
-      </c>
-      <c r="M14" t="s">
+      <c r="O14" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>136</v>
+      </c>
+      <c r="R14" t="s">
         <v>157</v>
       </c>
-      <c r="N14" t="s">
+      <c r="S14" t="s">
         <v>158</v>
       </c>
-      <c r="O14" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>136</v>
-      </c>
-      <c r="R14" t="s">
-        <v>159</v>
-      </c>
-      <c r="S14" t="s">
-        <v>160</v>
-      </c>
       <c r="T14" t="s">
         <v>18</v>
       </c>
@@ -6114,10 +6114,10 @@
         <v>136</v>
       </c>
       <c r="W14" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="X14" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="Y14" t="s">
         <v>19</v>
@@ -6128,10 +6128,10 @@
         <v>136</v>
       </c>
       <c r="C15" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D15" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E15" t="s">
         <v>11</v>
@@ -6140,23 +6140,23 @@
         <v>136</v>
       </c>
       <c r="H15" t="s">
+        <v>159</v>
+      </c>
+      <c r="I15" t="s">
+        <v>160</v>
+      </c>
+      <c r="J15" t="s">
+        <v>14</v>
+      </c>
+      <c r="L15" t="s">
+        <v>136</v>
+      </c>
+      <c r="M15" t="s">
         <v>161</v>
       </c>
-      <c r="I15" t="s">
+      <c r="N15" t="s">
         <v>162</v>
       </c>
-      <c r="J15" t="s">
-        <v>14</v>
-      </c>
-      <c r="L15" t="s">
-        <v>136</v>
-      </c>
-      <c r="M15" t="s">
-        <v>163</v>
-      </c>
-      <c r="N15" t="s">
-        <v>164</v>
-      </c>
       <c r="O15" t="s">
         <v>17</v>
       </c>
@@ -6164,10 +6164,10 @@
         <v>136</v>
       </c>
       <c r="R15" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="S15" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="T15" t="s">
         <v>18</v>
@@ -6176,10 +6176,10 @@
         <v>136</v>
       </c>
       <c r="W15" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="X15" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y15" t="s">
         <v>19</v>
@@ -6190,10 +6190,10 @@
         <v>136</v>
       </c>
       <c r="C16" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="D16" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="E16" t="s">
         <v>11</v>
@@ -6202,10 +6202,10 @@
         <v>136</v>
       </c>
       <c r="H16" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="I16" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J16" t="s">
         <v>14</v>
@@ -6214,10 +6214,10 @@
         <v>136</v>
       </c>
       <c r="M16" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="N16" t="s">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="O16" t="s">
         <v>17</v>
@@ -6226,10 +6226,10 @@
         <v>136</v>
       </c>
       <c r="R16" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="S16" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="T16" t="s">
         <v>18</v>
@@ -6238,10 +6238,10 @@
         <v>136</v>
       </c>
       <c r="W16" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="X16" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="Y16" t="s">
         <v>19</v>
@@ -6252,10 +6252,10 @@
         <v>136</v>
       </c>
       <c r="C17" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D17" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E17" t="s">
         <v>11</v>
@@ -6276,10 +6276,10 @@
         <v>136</v>
       </c>
       <c r="M17" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="N17" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="O17" t="s">
         <v>17</v>
@@ -6338,10 +6338,10 @@
         <v>136</v>
       </c>
       <c r="M18" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="O18" t="s">
         <v>17</v>
@@ -6350,10 +6350,10 @@
         <v>136</v>
       </c>
       <c r="R18" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="S18" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="T18" t="s">
         <v>18</v>
@@ -6362,10 +6362,10 @@
         <v>136</v>
       </c>
       <c r="W18" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="X18" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Y18" t="s">
         <v>19</v>
@@ -6388,10 +6388,10 @@
         <v>136</v>
       </c>
       <c r="H19" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I19" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="J19" t="s">
         <v>14</v>
@@ -6400,10 +6400,10 @@
         <v>136</v>
       </c>
       <c r="M19" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="N19" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="O19" t="s">
         <v>17</v>
@@ -6412,10 +6412,10 @@
         <v>136</v>
       </c>
       <c r="R19" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="S19" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="T19" t="s">
         <v>18</v>
@@ -6424,10 +6424,10 @@
         <v>136</v>
       </c>
       <c r="W19" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="X19" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="Y19" t="s">
         <v>19</v>
@@ -6438,10 +6438,10 @@
         <v>136</v>
       </c>
       <c r="C20" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D20" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E20" t="s">
         <v>11</v>
@@ -6450,10 +6450,10 @@
         <v>136</v>
       </c>
       <c r="H20" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I20" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J20" t="s">
         <v>14</v>
@@ -6462,10 +6462,10 @@
         <v>136</v>
       </c>
       <c r="M20" t="s">
-        <v>175</v>
+        <v>143</v>
       </c>
       <c r="N20" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="O20" t="s">
         <v>17</v>
@@ -6474,10 +6474,10 @@
         <v>136</v>
       </c>
       <c r="R20" t="s">
-        <v>141</v>
+        <v>179</v>
       </c>
       <c r="S20" t="s">
-        <v>142</v>
+        <v>180</v>
       </c>
       <c r="T20" t="s">
         <v>18</v>
@@ -6486,10 +6486,10 @@
         <v>136</v>
       </c>
       <c r="W20" t="s">
-        <v>141</v>
+        <v>179</v>
       </c>
       <c r="X20" t="s">
-        <v>142</v>
+        <v>180</v>
       </c>
       <c r="Y20" t="s">
         <v>19</v>
@@ -6500,10 +6500,10 @@
         <v>136</v>
       </c>
       <c r="C21" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D21" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E21" t="s">
         <v>11</v>
@@ -6512,10 +6512,10 @@
         <v>136</v>
       </c>
       <c r="H21" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="I21" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="J21" t="s">
         <v>14</v>
@@ -6524,10 +6524,10 @@
         <v>136</v>
       </c>
       <c r="M21" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="N21" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="O21" t="s">
         <v>17</v>
@@ -6536,10 +6536,10 @@
         <v>136</v>
       </c>
       <c r="R21" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="S21" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="T21" t="s">
         <v>18</v>
@@ -6548,10 +6548,10 @@
         <v>136</v>
       </c>
       <c r="W21" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="X21" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="Y21" t="s">
         <v>19</v>
@@ -6562,10 +6562,10 @@
         <v>136</v>
       </c>
       <c r="C22" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="D22" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="E22" t="s">
         <v>11</v>
@@ -6586,10 +6586,10 @@
         <v>136</v>
       </c>
       <c r="M22" t="s">
-        <v>181</v>
+        <v>139</v>
       </c>
       <c r="N22" t="s">
-        <v>182</v>
+        <v>140</v>
       </c>
       <c r="O22" t="s">
         <v>17</v>
@@ -6598,10 +6598,10 @@
         <v>136</v>
       </c>
       <c r="R22" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="S22" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="T22" t="s">
         <v>18</v>
@@ -6610,10 +6610,10 @@
         <v>136</v>
       </c>
       <c r="W22" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="X22" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="Y22" t="s">
         <v>19</v>
@@ -6624,10 +6624,10 @@
         <v>136</v>
       </c>
       <c r="C23" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D23" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E23" t="s">
         <v>11</v>
@@ -6636,10 +6636,10 @@
         <v>136</v>
       </c>
       <c r="H23" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="I23" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="J23" t="s">
         <v>14</v>
@@ -6648,10 +6648,10 @@
         <v>136</v>
       </c>
       <c r="M23" t="s">
-        <v>183</v>
+        <v>145</v>
       </c>
       <c r="N23" t="s">
-        <v>184</v>
+        <v>146</v>
       </c>
       <c r="O23" t="s">
         <v>17</v>
@@ -6660,10 +6660,10 @@
         <v>136</v>
       </c>
       <c r="R23" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="S23" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="T23" t="s">
         <v>18</v>
@@ -6672,10 +6672,10 @@
         <v>136</v>
       </c>
       <c r="W23" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="X23" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="Y23" t="s">
         <v>19</v>
@@ -6698,10 +6698,10 @@
         <v>136</v>
       </c>
       <c r="H24" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="I24" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="J24" t="s">
         <v>14</v>
@@ -6710,10 +6710,10 @@
         <v>136</v>
       </c>
       <c r="M24" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="N24" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="O24" t="s">
         <v>17</v>
@@ -6722,10 +6722,10 @@
         <v>136</v>
       </c>
       <c r="R24" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="S24" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="T24" t="s">
         <v>18</v>
@@ -6734,10 +6734,10 @@
         <v>136</v>
       </c>
       <c r="W24" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="X24" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="Y24" t="s">
         <v>19</v>
@@ -6760,10 +6760,10 @@
         <v>136</v>
       </c>
       <c r="H25" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I25" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J25" t="s">
         <v>14</v>
@@ -6772,10 +6772,10 @@
         <v>136</v>
       </c>
       <c r="M25" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="N25" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="O25" t="s">
         <v>17</v>
@@ -6784,10 +6784,10 @@
         <v>136</v>
       </c>
       <c r="R25" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="S25" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="T25" t="s">
         <v>18</v>
@@ -6796,10 +6796,10 @@
         <v>136</v>
       </c>
       <c r="W25" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="X25" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="Y25" t="s">
         <v>19</v>
@@ -6810,10 +6810,10 @@
         <v>136</v>
       </c>
       <c r="C26" t="s">
-        <v>141</v>
+        <v>179</v>
       </c>
       <c r="D26" t="s">
-        <v>142</v>
+        <v>180</v>
       </c>
       <c r="E26" t="s">
         <v>11</v>
@@ -6834,10 +6834,10 @@
         <v>136</v>
       </c>
       <c r="M26" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="O26" t="s">
         <v>17</v>
@@ -6846,10 +6846,10 @@
         <v>136</v>
       </c>
       <c r="R26" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="S26" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="T26" t="s">
         <v>18</v>
@@ -6858,10 +6858,10 @@
         <v>136</v>
       </c>
       <c r="W26" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="X26" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Y26" t="s">
         <v>19</v>
@@ -6872,10 +6872,10 @@
         <v>136</v>
       </c>
       <c r="C27" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D27" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E27" t="s">
         <v>11</v>
@@ -6884,35 +6884,35 @@
         <v>136</v>
       </c>
       <c r="H27" t="s">
+        <v>177</v>
+      </c>
+      <c r="I27" t="s">
+        <v>178</v>
+      </c>
+      <c r="J27" t="s">
+        <v>14</v>
+      </c>
+      <c r="L27" t="s">
+        <v>136</v>
+      </c>
+      <c r="M27" t="s">
         <v>191</v>
       </c>
-      <c r="I27" t="s">
+      <c r="N27" t="s">
         <v>192</v>
       </c>
-      <c r="J27" t="s">
-        <v>14</v>
-      </c>
-      <c r="L27" t="s">
-        <v>136</v>
-      </c>
-      <c r="M27" t="s">
+      <c r="O27" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>136</v>
+      </c>
+      <c r="R27" t="s">
         <v>193</v>
       </c>
-      <c r="N27" t="s">
+      <c r="S27" t="s">
         <v>194</v>
       </c>
-      <c r="O27" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>136</v>
-      </c>
-      <c r="R27" t="s">
-        <v>195</v>
-      </c>
-      <c r="S27" t="s">
-        <v>196</v>
-      </c>
       <c r="T27" t="s">
         <v>18</v>
       </c>
@@ -6920,10 +6920,10 @@
         <v>136</v>
       </c>
       <c r="W27" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="X27" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="Y27" t="s">
         <v>19</v>
@@ -6934,10 +6934,10 @@
         <v>136</v>
       </c>
       <c r="C28" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D28" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E28" t="s">
         <v>11</v>
@@ -6946,10 +6946,10 @@
         <v>136</v>
       </c>
       <c r="H28" t="s">
-        <v>141</v>
+        <v>179</v>
       </c>
       <c r="I28" t="s">
-        <v>142</v>
+        <v>180</v>
       </c>
       <c r="J28" t="s">
         <v>14</v>
@@ -6958,10 +6958,10 @@
         <v>136</v>
       </c>
       <c r="M28" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N28" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="O28" t="s">
         <v>17</v>
@@ -6996,10 +6996,10 @@
         <v>136</v>
       </c>
       <c r="C29" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="D29" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="E29" t="s">
         <v>11</v>
@@ -7008,10 +7008,10 @@
         <v>136</v>
       </c>
       <c r="H29" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="I29" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J29" t="s">
         <v>14</v>
@@ -7020,10 +7020,10 @@
         <v>136</v>
       </c>
       <c r="M29" t="s">
-        <v>145</v>
+        <v>197</v>
       </c>
       <c r="N29" t="s">
-        <v>146</v>
+        <v>198</v>
       </c>
       <c r="O29" t="s">
         <v>17</v>
@@ -7058,10 +7058,10 @@
         <v>136</v>
       </c>
       <c r="C30" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D30" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E30" t="s">
         <v>11</v>
@@ -7070,10 +7070,10 @@
         <v>136</v>
       </c>
       <c r="H30" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I30" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="J30" t="s">
         <v>14</v>
@@ -7082,10 +7082,10 @@
         <v>136</v>
       </c>
       <c r="M30" t="s">
-        <v>195</v>
+        <v>149</v>
       </c>
       <c r="N30" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="O30" t="s">
         <v>17</v>
@@ -7094,10 +7094,10 @@
         <v>136</v>
       </c>
       <c r="R30" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="S30" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="T30" t="s">
         <v>18</v>
@@ -7106,10 +7106,10 @@
         <v>136</v>
       </c>
       <c r="W30" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="X30" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="Y30" t="s">
         <v>19</v>
@@ -7120,10 +7120,10 @@
         <v>136</v>
       </c>
       <c r="C31" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D31" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="E31" t="s">
         <v>11</v>
@@ -7132,10 +7132,10 @@
         <v>136</v>
       </c>
       <c r="H31" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="I31" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="J31" t="s">
         <v>14</v>
@@ -7144,10 +7144,10 @@
         <v>136</v>
       </c>
       <c r="M31" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="N31" t="s">
-        <v>166</v>
+        <v>200</v>
       </c>
       <c r="O31" t="s">
         <v>17</v>
@@ -7156,10 +7156,10 @@
         <v>136</v>
       </c>
       <c r="R31" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="S31" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="T31" t="s">
         <v>18</v>
@@ -7168,10 +7168,10 @@
         <v>136</v>
       </c>
       <c r="W31" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="X31" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="Y31" t="s">
         <v>19</v>
@@ -7182,10 +7182,10 @@
         <v>136</v>
       </c>
       <c r="C32" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D32" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E32" t="s">
         <v>11</v>
@@ -7194,10 +7194,10 @@
         <v>136</v>
       </c>
       <c r="H32" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="I32" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="J32" t="s">
         <v>14</v>
@@ -7206,10 +7206,10 @@
         <v>136</v>
       </c>
       <c r="M32" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="N32" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="O32" t="s">
         <v>17</v>
@@ -7218,10 +7218,10 @@
         <v>136</v>
       </c>
       <c r="R32" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="S32" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="T32" t="s">
         <v>18</v>
@@ -7230,10 +7230,10 @@
         <v>136</v>
       </c>
       <c r="W32" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="X32" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="Y32" t="s">
         <v>19</v>
@@ -7244,10 +7244,10 @@
         <v>136</v>
       </c>
       <c r="C33" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D33" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E33" t="s">
         <v>11</v>
@@ -7256,10 +7256,10 @@
         <v>136</v>
       </c>
       <c r="H33" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="I33" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="J33" t="s">
         <v>14</v>
@@ -7268,10 +7268,10 @@
         <v>136</v>
       </c>
       <c r="M33" t="s">
-        <v>199</v>
+        <v>147</v>
       </c>
       <c r="N33" t="s">
-        <v>200</v>
+        <v>148</v>
       </c>
       <c r="O33" t="s">
         <v>17</v>
@@ -7306,10 +7306,10 @@
         <v>136</v>
       </c>
       <c r="H34" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="I34" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="J34" t="s">
         <v>14</v>
@@ -7318,10 +7318,10 @@
         <v>136</v>
       </c>
       <c r="M34" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="N34" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="O34" t="s">
         <v>17</v>
@@ -7330,10 +7330,10 @@
         <v>136</v>
       </c>
       <c r="R34" t="s">
-        <v>201</v>
+        <v>165</v>
       </c>
       <c r="S34" t="s">
-        <v>202</v>
+        <v>166</v>
       </c>
       <c r="T34" t="s">
         <v>18</v>
@@ -7342,10 +7342,10 @@
         <v>136</v>
       </c>
       <c r="W34" t="s">
-        <v>201</v>
+        <v>165</v>
       </c>
       <c r="X34" t="s">
-        <v>202</v>
+        <v>166</v>
       </c>
       <c r="Y34" t="s">
         <v>19</v>
@@ -7356,23 +7356,23 @@
         <v>136</v>
       </c>
       <c r="H35" t="s">
+        <v>161</v>
+      </c>
+      <c r="I35" t="s">
+        <v>162</v>
+      </c>
+      <c r="J35" t="s">
+        <v>14</v>
+      </c>
+      <c r="L35" t="s">
+        <v>136</v>
+      </c>
+      <c r="M35" t="s">
         <v>203</v>
       </c>
-      <c r="I35" t="s">
+      <c r="N35" t="s">
         <v>204</v>
       </c>
-      <c r="J35" t="s">
-        <v>14</v>
-      </c>
-      <c r="L35" t="s">
-        <v>136</v>
-      </c>
-      <c r="M35" t="s">
-        <v>151</v>
-      </c>
-      <c r="N35" t="s">
-        <v>152</v>
-      </c>
       <c r="O35" t="s">
         <v>17</v>
       </c>
@@ -7380,10 +7380,10 @@
         <v>136</v>
       </c>
       <c r="R35" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="S35" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="T35" t="s">
         <v>18</v>
@@ -7392,10 +7392,10 @@
         <v>136</v>
       </c>
       <c r="W35" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="X35" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="Y35" t="s">
         <v>19</v>
@@ -7406,23 +7406,23 @@
         <v>136</v>
       </c>
       <c r="H36" t="s">
+        <v>195</v>
+      </c>
+      <c r="I36" t="s">
+        <v>196</v>
+      </c>
+      <c r="J36" t="s">
+        <v>14</v>
+      </c>
+      <c r="L36" t="s">
+        <v>136</v>
+      </c>
+      <c r="M36" t="s">
         <v>205</v>
       </c>
-      <c r="I36" t="s">
+      <c r="N36" t="s">
         <v>206</v>
       </c>
-      <c r="J36" t="s">
-        <v>14</v>
-      </c>
-      <c r="L36" t="s">
-        <v>136</v>
-      </c>
-      <c r="M36" t="s">
-        <v>167</v>
-      </c>
-      <c r="N36" t="s">
-        <v>168</v>
-      </c>
       <c r="O36" t="s">
         <v>17</v>
       </c>
@@ -7430,10 +7430,10 @@
         <v>136</v>
       </c>
       <c r="R36" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="S36" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="T36" t="s">
         <v>18</v>
@@ -7442,10 +7442,10 @@
         <v>136</v>
       </c>
       <c r="W36" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="X36" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="Y36" t="s">
         <v>19</v>
@@ -7456,10 +7456,10 @@
         <v>136</v>
       </c>
       <c r="H37" t="s">
-        <v>147</v>
+        <v>207</v>
       </c>
       <c r="I37" t="s">
-        <v>148</v>
+        <v>208</v>
       </c>
       <c r="J37" t="s">
         <v>14</v>
@@ -7468,10 +7468,10 @@
         <v>136</v>
       </c>
       <c r="M37" t="s">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="N37" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="O37" t="s">
         <v>17</v>
@@ -7480,10 +7480,10 @@
         <v>136</v>
       </c>
       <c r="R37" t="s">
-        <v>163</v>
+        <v>209</v>
       </c>
       <c r="S37" t="s">
-        <v>164</v>
+        <v>210</v>
       </c>
       <c r="T37" t="s">
         <v>18</v>
@@ -7492,10 +7492,10 @@
         <v>136</v>
       </c>
       <c r="W37" t="s">
-        <v>163</v>
+        <v>209</v>
       </c>
       <c r="X37" t="s">
-        <v>164</v>
+        <v>210</v>
       </c>
       <c r="Y37" t="s">
         <v>19</v>
@@ -7506,10 +7506,10 @@
         <v>136</v>
       </c>
       <c r="H38" t="s">
-        <v>201</v>
+        <v>165</v>
       </c>
       <c r="I38" t="s">
-        <v>202</v>
+        <v>166</v>
       </c>
       <c r="J38" t="s">
         <v>14</v>
@@ -7518,10 +7518,10 @@
         <v>136</v>
       </c>
       <c r="M38" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="N38" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="O38" t="s">
         <v>17</v>
@@ -7530,10 +7530,10 @@
         <v>136</v>
       </c>
       <c r="R38" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="S38" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="T38" t="s">
         <v>18</v>
@@ -7542,10 +7542,10 @@
         <v>136</v>
       </c>
       <c r="W38" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="X38" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="Y38" t="s">
         <v>19</v>
@@ -7556,10 +7556,10 @@
         <v>136</v>
       </c>
       <c r="H39" t="s">
-        <v>163</v>
+        <v>209</v>
       </c>
       <c r="I39" t="s">
-        <v>164</v>
+        <v>210</v>
       </c>
       <c r="J39" t="s">
         <v>14</v>
@@ -7568,10 +7568,10 @@
         <v>136</v>
       </c>
       <c r="M39" t="s">
-        <v>143</v>
+        <v>185</v>
       </c>
       <c r="N39" t="s">
-        <v>144</v>
+        <v>186</v>
       </c>
       <c r="O39" t="s">
         <v>17</v>
@@ -7582,10 +7582,10 @@
         <v>136</v>
       </c>
       <c r="H40" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I40" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="J40" t="s">
         <v>14</v>
@@ -7594,10 +7594,10 @@
         <v>136</v>
       </c>
       <c r="M40" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="N40" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="O40" t="s">
         <v>17</v>
@@ -7608,10 +7608,10 @@
         <v>136</v>
       </c>
       <c r="H41" t="s">
-        <v>157</v>
+        <v>203</v>
       </c>
       <c r="I41" t="s">
-        <v>158</v>
+        <v>204</v>
       </c>
       <c r="J41" t="s">
         <v>14</v>
@@ -7620,10 +7620,10 @@
         <v>136</v>
       </c>
       <c r="M41" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="N41" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="O41" t="s">
         <v>17</v>
@@ -7634,10 +7634,10 @@
         <v>136</v>
       </c>
       <c r="M42" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="N42" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="O42" t="s">
         <v>17</v>
@@ -7648,10 +7648,10 @@
         <v>136</v>
       </c>
       <c r="M43" t="s">
-        <v>201</v>
+        <v>157</v>
       </c>
       <c r="N43" t="s">
-        <v>202</v>
+        <v>158</v>
       </c>
       <c r="O43" t="s">
         <v>17</v>
@@ -7662,10 +7662,10 @@
         <v>136</v>
       </c>
       <c r="M44" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="N44" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O44" t="s">
         <v>17</v>
@@ -7676,10 +7676,10 @@
         <v>136</v>
       </c>
       <c r="M45" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="N45" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="O45" t="s">
         <v>17</v>
@@ -7690,10 +7690,10 @@
         <v>136</v>
       </c>
       <c r="M46" t="s">
-        <v>205</v>
+        <v>159</v>
       </c>
       <c r="N46" t="s">
-        <v>206</v>
+        <v>160</v>
       </c>
       <c r="O46" t="s">
         <v>17</v>
@@ -7704,10 +7704,10 @@
         <v>136</v>
       </c>
       <c r="M47" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="N47" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="O47" t="s">
         <v>17</v>
@@ -7719,7 +7719,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E08E1C8D-A1DF-4721-A9D1-38E238E8D015}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5A9E5E4-7772-440C-BBFC-5ED6DEA5909F}">
   <dimension ref="B9:Y33"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7931,10 +7931,10 @@
         <v>211</v>
       </c>
       <c r="C13" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="D13" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
@@ -7943,10 +7943,10 @@
         <v>211</v>
       </c>
       <c r="H13" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="I13" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="J13" t="s">
         <v>14</v>
@@ -7955,10 +7955,10 @@
         <v>211</v>
       </c>
       <c r="M13" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="N13" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="O13" t="s">
         <v>17</v>
@@ -7967,10 +7967,10 @@
         <v>211</v>
       </c>
       <c r="R13" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="S13" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="T13" t="s">
         <v>18</v>
@@ -7979,10 +7979,10 @@
         <v>211</v>
       </c>
       <c r="W13" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="X13" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="Y13" t="s">
         <v>19</v>
@@ -7993,10 +7993,10 @@
         <v>211</v>
       </c>
       <c r="H14" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="I14" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="J14" t="s">
         <v>14</v>
@@ -8005,10 +8005,10 @@
         <v>211</v>
       </c>
       <c r="M14" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="N14" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="O14" t="s">
         <v>17</v>
@@ -8093,10 +8093,10 @@
         <v>211</v>
       </c>
       <c r="H16" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="I16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="J16" t="s">
         <v>14</v>
@@ -8105,10 +8105,10 @@
         <v>211</v>
       </c>
       <c r="M16" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="N16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="O16" t="s">
         <v>17</v>
@@ -8117,10 +8117,10 @@
         <v>211</v>
       </c>
       <c r="R16" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="S16" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="T16" t="s">
         <v>18</v>
@@ -8129,10 +8129,10 @@
         <v>211</v>
       </c>
       <c r="W16" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="X16" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Y16" t="s">
         <v>19</v>
@@ -8143,10 +8143,10 @@
         <v>211</v>
       </c>
       <c r="H17" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="I17" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="J17" t="s">
         <v>14</v>
@@ -8155,10 +8155,10 @@
         <v>211</v>
       </c>
       <c r="M17" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="N17" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="O17" t="s">
         <v>17</v>
@@ -8167,10 +8167,10 @@
         <v>211</v>
       </c>
       <c r="R17" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="S17" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="T17" t="s">
         <v>18</v>
@@ -8179,10 +8179,10 @@
         <v>211</v>
       </c>
       <c r="W17" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="X17" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="Y17" t="s">
         <v>19</v>
@@ -8193,10 +8193,10 @@
         <v>211</v>
       </c>
       <c r="H18" t="s">
-        <v>214</v>
+        <v>240</v>
       </c>
       <c r="I18" t="s">
-        <v>215</v>
+        <v>241</v>
       </c>
       <c r="J18" t="s">
         <v>14</v>
@@ -8205,10 +8205,10 @@
         <v>211</v>
       </c>
       <c r="M18" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="N18" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="O18" t="s">
         <v>17</v>
@@ -8217,10 +8217,10 @@
         <v>211</v>
       </c>
       <c r="R18" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="S18" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="T18" t="s">
         <v>18</v>
@@ -8229,10 +8229,10 @@
         <v>211</v>
       </c>
       <c r="W18" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="X18" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="Y18" t="s">
         <v>19</v>
@@ -8267,10 +8267,10 @@
         <v>211</v>
       </c>
       <c r="R19" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="S19" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="T19" t="s">
         <v>18</v>
@@ -8279,10 +8279,10 @@
         <v>211</v>
       </c>
       <c r="W19" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="X19" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="Y19" t="s">
         <v>19</v>
@@ -8293,10 +8293,10 @@
         <v>211</v>
       </c>
       <c r="H20" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="I20" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J20" t="s">
         <v>14</v>
@@ -8305,10 +8305,10 @@
         <v>211</v>
       </c>
       <c r="M20" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="N20" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="O20" t="s">
         <v>17</v>
@@ -8319,10 +8319,10 @@
         <v>211</v>
       </c>
       <c r="H21" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I21" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="J21" t="s">
         <v>14</v>
@@ -8331,10 +8331,10 @@
         <v>211</v>
       </c>
       <c r="M21" t="s">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="N21" t="s">
-        <v>217</v>
+        <v>241</v>
       </c>
       <c r="O21" t="s">
         <v>17</v>
@@ -8345,10 +8345,10 @@
         <v>211</v>
       </c>
       <c r="H22" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="I22" t="s">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="J22" t="s">
         <v>14</v>
@@ -8357,10 +8357,10 @@
         <v>211</v>
       </c>
       <c r="M22" t="s">
-        <v>246</v>
+        <v>216</v>
       </c>
       <c r="N22" t="s">
-        <v>247</v>
+        <v>217</v>
       </c>
       <c r="O22" t="s">
         <v>17</v>
@@ -8371,10 +8371,10 @@
         <v>211</v>
       </c>
       <c r="H23" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="I23" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="J23" t="s">
         <v>14</v>
@@ -8383,10 +8383,10 @@
         <v>211</v>
       </c>
       <c r="M23" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="N23" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="O23" t="s">
         <v>17</v>
@@ -8397,10 +8397,10 @@
         <v>211</v>
       </c>
       <c r="H24" t="s">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="I24" t="s">
-        <v>249</v>
+        <v>223</v>
       </c>
       <c r="J24" t="s">
         <v>14</v>
@@ -8409,10 +8409,10 @@
         <v>211</v>
       </c>
       <c r="M24" t="s">
-        <v>226</v>
+        <v>250</v>
       </c>
       <c r="N24" t="s">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="O24" t="s">
         <v>17</v>
@@ -8437,10 +8437,10 @@
         <v>211</v>
       </c>
       <c r="M26" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="N26" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="O26" t="s">
         <v>17</v>
@@ -8451,10 +8451,10 @@
         <v>211</v>
       </c>
       <c r="M27" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="N27" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="O27" t="s">
         <v>17</v>
@@ -8479,10 +8479,10 @@
         <v>211</v>
       </c>
       <c r="M29" t="s">
-        <v>254</v>
+        <v>230</v>
       </c>
       <c r="N29" t="s">
-        <v>255</v>
+        <v>231</v>
       </c>
       <c r="O29" t="s">
         <v>17</v>
@@ -8493,10 +8493,10 @@
         <v>211</v>
       </c>
       <c r="M30" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="N30" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="O30" t="s">
         <v>17</v>
@@ -8507,10 +8507,10 @@
         <v>211</v>
       </c>
       <c r="M31" t="s">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="N31" t="s">
-        <v>239</v>
+        <v>213</v>
       </c>
       <c r="O31" t="s">
         <v>17</v>
@@ -8521,10 +8521,10 @@
         <v>211</v>
       </c>
       <c r="M32" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="N32" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="O32" t="s">
         <v>17</v>
@@ -8535,10 +8535,10 @@
         <v>211</v>
       </c>
       <c r="M33" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="N33" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="O33" t="s">
         <v>17</v>
@@ -8550,7 +8550,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7783ED6F-3CC6-463D-8404-976DDF62484A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{695B4A73-B0F7-4859-A8A8-8397A77E01AB}">
   <dimension ref="B9:Y35"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -8724,10 +8724,10 @@
         <v>258</v>
       </c>
       <c r="M12" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N12" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O12" t="s">
         <v>17</v>
@@ -8762,10 +8762,10 @@
         <v>258</v>
       </c>
       <c r="C13" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D13" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
@@ -8786,10 +8786,10 @@
         <v>258</v>
       </c>
       <c r="M13" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="N13" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O13" t="s">
         <v>17</v>
@@ -8798,10 +8798,10 @@
         <v>258</v>
       </c>
       <c r="R13" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="S13" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="T13" t="s">
         <v>18</v>
@@ -8810,10 +8810,10 @@
         <v>258</v>
       </c>
       <c r="W13" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="X13" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Y13" t="s">
         <v>19</v>
@@ -8836,10 +8836,10 @@
         <v>258</v>
       </c>
       <c r="H14" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="I14" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="J14" t="s">
         <v>14</v>
@@ -8848,10 +8848,10 @@
         <v>258</v>
       </c>
       <c r="M14" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="N14" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="O14" t="s">
         <v>17</v>
@@ -8860,10 +8860,10 @@
         <v>258</v>
       </c>
       <c r="R14" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="S14" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="T14" t="s">
         <v>18</v>
@@ -8872,10 +8872,10 @@
         <v>258</v>
       </c>
       <c r="W14" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="X14" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="Y14" t="s">
         <v>19</v>
@@ -8898,10 +8898,10 @@
         <v>258</v>
       </c>
       <c r="H15" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="I15" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="J15" t="s">
         <v>14</v>
@@ -8910,10 +8910,10 @@
         <v>258</v>
       </c>
       <c r="M15" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="N15" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="O15" t="s">
         <v>17</v>
@@ -8922,10 +8922,10 @@
         <v>258</v>
       </c>
       <c r="R15" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="S15" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="T15" t="s">
         <v>18</v>
@@ -8934,10 +8934,10 @@
         <v>258</v>
       </c>
       <c r="W15" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="X15" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Y15" t="s">
         <v>19</v>
@@ -8948,10 +8948,10 @@
         <v>258</v>
       </c>
       <c r="C16" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="D16" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="E16" t="s">
         <v>11</v>
@@ -8960,10 +8960,10 @@
         <v>258</v>
       </c>
       <c r="H16" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="I16" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="J16" t="s">
         <v>14</v>
@@ -8972,10 +8972,10 @@
         <v>258</v>
       </c>
       <c r="M16" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="N16" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="O16" t="s">
         <v>17</v>
@@ -8984,10 +8984,10 @@
         <v>258</v>
       </c>
       <c r="R16" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="S16" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="T16" t="s">
         <v>18</v>
@@ -8996,10 +8996,10 @@
         <v>258</v>
       </c>
       <c r="W16" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="X16" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="Y16" t="s">
         <v>19</v>
@@ -9010,10 +9010,10 @@
         <v>258</v>
       </c>
       <c r="C17" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D17" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E17" t="s">
         <v>11</v>
@@ -9072,10 +9072,10 @@
         <v>258</v>
       </c>
       <c r="C18" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D18" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E18" t="s">
         <v>11</v>
@@ -9084,10 +9084,10 @@
         <v>258</v>
       </c>
       <c r="H18" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="I18" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="J18" t="s">
         <v>14</v>
@@ -9096,10 +9096,10 @@
         <v>258</v>
       </c>
       <c r="M18" t="s">
-        <v>287</v>
+        <v>259</v>
       </c>
       <c r="N18" t="s">
-        <v>288</v>
+        <v>260</v>
       </c>
       <c r="O18" t="s">
         <v>17</v>
@@ -9108,10 +9108,10 @@
         <v>258</v>
       </c>
       <c r="R18" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="S18" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="T18" t="s">
         <v>18</v>
@@ -9120,10 +9120,10 @@
         <v>258</v>
       </c>
       <c r="W18" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="X18" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="Y18" t="s">
         <v>19</v>
@@ -9134,10 +9134,10 @@
         <v>258</v>
       </c>
       <c r="C19" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D19" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E19" t="s">
         <v>11</v>
@@ -9146,10 +9146,10 @@
         <v>258</v>
       </c>
       <c r="H19" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I19" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="J19" t="s">
         <v>14</v>
@@ -9158,10 +9158,10 @@
         <v>258</v>
       </c>
       <c r="M19" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="N19" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="O19" t="s">
         <v>17</v>
@@ -9170,10 +9170,10 @@
         <v>258</v>
       </c>
       <c r="R19" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="S19" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="T19" t="s">
         <v>18</v>
@@ -9182,10 +9182,10 @@
         <v>258</v>
       </c>
       <c r="W19" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="X19" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Y19" t="s">
         <v>19</v>
@@ -9196,10 +9196,10 @@
         <v>258</v>
       </c>
       <c r="C20" t="s">
-        <v>263</v>
+        <v>289</v>
       </c>
       <c r="D20" t="s">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="E20" t="s">
         <v>11</v>
@@ -9208,10 +9208,10 @@
         <v>258</v>
       </c>
       <c r="H20" t="s">
-        <v>263</v>
+        <v>289</v>
       </c>
       <c r="I20" t="s">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="J20" t="s">
         <v>14</v>
@@ -9220,10 +9220,10 @@
         <v>258</v>
       </c>
       <c r="M20" t="s">
-        <v>265</v>
+        <v>291</v>
       </c>
       <c r="N20" t="s">
-        <v>266</v>
+        <v>292</v>
       </c>
       <c r="O20" t="s">
         <v>17</v>
@@ -9258,10 +9258,10 @@
         <v>258</v>
       </c>
       <c r="C21" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="E21" t="s">
         <v>11</v>
@@ -9270,10 +9270,10 @@
         <v>258</v>
       </c>
       <c r="H21" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="I21" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="J21" t="s">
         <v>14</v>
@@ -9282,10 +9282,10 @@
         <v>258</v>
       </c>
       <c r="M21" t="s">
-        <v>291</v>
+        <v>261</v>
       </c>
       <c r="N21" t="s">
-        <v>292</v>
+        <v>262</v>
       </c>
       <c r="O21" t="s">
         <v>17</v>
@@ -9294,10 +9294,10 @@
         <v>258</v>
       </c>
       <c r="R21" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="S21" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="T21" t="s">
         <v>18</v>
@@ -9306,10 +9306,10 @@
         <v>258</v>
       </c>
       <c r="W21" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="X21" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="Y21" t="s">
         <v>19</v>
@@ -9320,10 +9320,10 @@
         <v>258</v>
       </c>
       <c r="C22" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D22" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="E22" t="s">
         <v>11</v>
@@ -9332,10 +9332,10 @@
         <v>258</v>
       </c>
       <c r="H22" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="I22" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="J22" t="s">
         <v>14</v>
@@ -9344,10 +9344,10 @@
         <v>258</v>
       </c>
       <c r="M22" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="N22" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="O22" t="s">
         <v>17</v>
@@ -9356,10 +9356,10 @@
         <v>258</v>
       </c>
       <c r="R22" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="S22" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="T22" t="s">
         <v>18</v>
@@ -9368,10 +9368,10 @@
         <v>258</v>
       </c>
       <c r="W22" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="X22" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="Y22" t="s">
         <v>19</v>
@@ -9382,10 +9382,10 @@
         <v>258</v>
       </c>
       <c r="C23" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D23" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E23" t="s">
         <v>11</v>
@@ -9394,10 +9394,10 @@
         <v>258</v>
       </c>
       <c r="H23" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="I23" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J23" t="s">
         <v>14</v>
@@ -9406,10 +9406,10 @@
         <v>258</v>
       </c>
       <c r="M23" t="s">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="N23" t="s">
-        <v>278</v>
+        <v>298</v>
       </c>
       <c r="O23" t="s">
         <v>17</v>
@@ -9418,10 +9418,10 @@
         <v>258</v>
       </c>
       <c r="R23" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="S23" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="T23" t="s">
         <v>18</v>
@@ -9430,10 +9430,10 @@
         <v>258</v>
       </c>
       <c r="W23" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="X23" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Y23" t="s">
         <v>19</v>
@@ -9444,10 +9444,10 @@
         <v>258</v>
       </c>
       <c r="C24" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="D24" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="E24" t="s">
         <v>11</v>
@@ -9456,10 +9456,10 @@
         <v>258</v>
       </c>
       <c r="H24" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="I24" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="J24" t="s">
         <v>14</v>
@@ -9468,10 +9468,10 @@
         <v>258</v>
       </c>
       <c r="M24" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="N24" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="O24" t="s">
         <v>17</v>
@@ -9480,10 +9480,10 @@
         <v>258</v>
       </c>
       <c r="R24" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="S24" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="T24" t="s">
         <v>18</v>
@@ -9492,10 +9492,10 @@
         <v>258</v>
       </c>
       <c r="W24" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="X24" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="Y24" t="s">
         <v>19</v>
@@ -9506,10 +9506,10 @@
         <v>258</v>
       </c>
       <c r="C25" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="D25" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="E25" t="s">
         <v>11</v>
@@ -9518,10 +9518,10 @@
         <v>258</v>
       </c>
       <c r="H25" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="I25" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="J25" t="s">
         <v>14</v>
@@ -9530,10 +9530,10 @@
         <v>258</v>
       </c>
       <c r="M25" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="N25" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="O25" t="s">
         <v>17</v>
@@ -9542,10 +9542,10 @@
         <v>258</v>
       </c>
       <c r="R25" t="s">
-        <v>263</v>
+        <v>289</v>
       </c>
       <c r="S25" t="s">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="T25" t="s">
         <v>18</v>
@@ -9554,10 +9554,10 @@
         <v>258</v>
       </c>
       <c r="W25" t="s">
-        <v>263</v>
+        <v>289</v>
       </c>
       <c r="X25" t="s">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="Y25" t="s">
         <v>19</v>
@@ -9568,10 +9568,10 @@
         <v>258</v>
       </c>
       <c r="C26" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="D26" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="E26" t="s">
         <v>11</v>
@@ -9580,10 +9580,10 @@
         <v>258</v>
       </c>
       <c r="H26" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="I26" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="J26" t="s">
         <v>14</v>
@@ -9592,10 +9592,10 @@
         <v>258</v>
       </c>
       <c r="M26" t="s">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="N26" t="s">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="O26" t="s">
         <v>17</v>
@@ -9604,10 +9604,10 @@
         <v>258</v>
       </c>
       <c r="R26" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="S26" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="T26" t="s">
         <v>18</v>
@@ -9616,10 +9616,10 @@
         <v>258</v>
       </c>
       <c r="W26" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="X26" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="Y26" t="s">
         <v>19</v>
@@ -9630,10 +9630,10 @@
         <v>258</v>
       </c>
       <c r="C27" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="E27" t="s">
         <v>11</v>
@@ -9642,10 +9642,10 @@
         <v>258</v>
       </c>
       <c r="H27" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="I27" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="J27" t="s">
         <v>14</v>
@@ -9654,10 +9654,10 @@
         <v>258</v>
       </c>
       <c r="M27" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="N27" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="O27" t="s">
         <v>17</v>
@@ -9666,10 +9666,10 @@
         <v>258</v>
       </c>
       <c r="R27" t="s">
-        <v>299</v>
+        <v>273</v>
       </c>
       <c r="S27" t="s">
-        <v>300</v>
+        <v>274</v>
       </c>
       <c r="T27" t="s">
         <v>18</v>
@@ -9678,10 +9678,10 @@
         <v>258</v>
       </c>
       <c r="W27" t="s">
-        <v>299</v>
+        <v>273</v>
       </c>
       <c r="X27" t="s">
-        <v>300</v>
+        <v>274</v>
       </c>
       <c r="Y27" t="s">
         <v>19</v>
@@ -9692,10 +9692,10 @@
         <v>258</v>
       </c>
       <c r="C28" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="D28" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="E28" t="s">
         <v>11</v>
@@ -9704,10 +9704,10 @@
         <v>258</v>
       </c>
       <c r="H28" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="I28" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="J28" t="s">
         <v>14</v>
@@ -9716,10 +9716,10 @@
         <v>258</v>
       </c>
       <c r="M28" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="N28" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="O28" t="s">
         <v>17</v>
@@ -9728,10 +9728,10 @@
         <v>258</v>
       </c>
       <c r="R28" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="S28" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="T28" t="s">
         <v>18</v>
@@ -9740,10 +9740,10 @@
         <v>258</v>
       </c>
       <c r="W28" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="X28" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="Y28" t="s">
         <v>19</v>
@@ -9754,10 +9754,10 @@
         <v>258</v>
       </c>
       <c r="C29" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="E29" t="s">
         <v>11</v>
@@ -9766,10 +9766,10 @@
         <v>258</v>
       </c>
       <c r="H29" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="I29" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="J29" t="s">
         <v>14</v>
@@ -9778,10 +9778,10 @@
         <v>258</v>
       </c>
       <c r="M29" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="N29" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="O29" t="s">
         <v>17</v>
@@ -9790,10 +9790,10 @@
         <v>258</v>
       </c>
       <c r="R29" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="S29" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="T29" t="s">
         <v>18</v>
@@ -9802,10 +9802,10 @@
         <v>258</v>
       </c>
       <c r="W29" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="X29" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="Y29" t="s">
         <v>19</v>
@@ -9816,10 +9816,10 @@
         <v>258</v>
       </c>
       <c r="H30" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="I30" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="J30" t="s">
         <v>14</v>
@@ -9828,10 +9828,10 @@
         <v>258</v>
       </c>
       <c r="M30" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="N30" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="O30" t="s">
         <v>17</v>
@@ -9840,10 +9840,10 @@
         <v>258</v>
       </c>
       <c r="R30" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="S30" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="T30" t="s">
         <v>18</v>
@@ -9852,10 +9852,10 @@
         <v>258</v>
       </c>
       <c r="W30" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="X30" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="Y30" t="s">
         <v>19</v>
@@ -9866,10 +9866,10 @@
         <v>258</v>
       </c>
       <c r="H31" t="s">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="I31" t="s">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="J31" t="s">
         <v>14</v>
@@ -9878,10 +9878,10 @@
         <v>258</v>
       </c>
       <c r="M31" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="N31" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="O31" t="s">
         <v>17</v>
@@ -9892,10 +9892,10 @@
         <v>258</v>
       </c>
       <c r="H32" t="s">
-        <v>271</v>
+        <v>297</v>
       </c>
       <c r="I32" t="s">
-        <v>272</v>
+        <v>298</v>
       </c>
       <c r="J32" t="s">
         <v>14</v>
@@ -9904,10 +9904,10 @@
         <v>258</v>
       </c>
       <c r="M32" t="s">
-        <v>261</v>
+        <v>305</v>
       </c>
       <c r="N32" t="s">
-        <v>262</v>
+        <v>306</v>
       </c>
       <c r="O32" t="s">
         <v>17</v>
@@ -9918,10 +9918,10 @@
         <v>258</v>
       </c>
       <c r="H33" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="I33" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="J33" t="s">
         <v>14</v>
@@ -9930,10 +9930,10 @@
         <v>258</v>
       </c>
       <c r="M33" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="N33" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="O33" t="s">
         <v>17</v>
@@ -9944,10 +9944,10 @@
         <v>258</v>
       </c>
       <c r="H34" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I34" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J34" t="s">
         <v>14</v>
@@ -9956,10 +9956,10 @@
         <v>258</v>
       </c>
       <c r="M34" t="s">
-        <v>303</v>
+        <v>265</v>
       </c>
       <c r="N34" t="s">
-        <v>304</v>
+        <v>266</v>
       </c>
       <c r="O34" t="s">
         <v>17</v>
@@ -9970,10 +9970,10 @@
         <v>258</v>
       </c>
       <c r="H35" t="s">
-        <v>299</v>
+        <v>273</v>
       </c>
       <c r="I35" t="s">
-        <v>300</v>
+        <v>274</v>
       </c>
       <c r="J35" t="s">
         <v>14</v>
@@ -9982,10 +9982,10 @@
         <v>258</v>
       </c>
       <c r="M35" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="N35" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="O35" t="s">
         <v>17</v>
@@ -9997,7 +9997,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F13C4B9F-48B8-4883-997E-9E08423A8C53}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B11EAAD0-54C1-48ED-A0A4-93DA5498E890}">
   <dimension ref="B9:Y27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -10209,10 +10209,10 @@
         <v>309</v>
       </c>
       <c r="C13" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D13" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
@@ -10233,10 +10233,10 @@
         <v>309</v>
       </c>
       <c r="M13" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="N13" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="O13" t="s">
         <v>17</v>
@@ -10245,10 +10245,10 @@
         <v>309</v>
       </c>
       <c r="R13" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="S13" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="T13" t="s">
         <v>18</v>
@@ -10257,10 +10257,10 @@
         <v>309</v>
       </c>
       <c r="W13" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="X13" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="Y13" t="s">
         <v>19</v>
@@ -10271,10 +10271,10 @@
         <v>309</v>
       </c>
       <c r="C14" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D14" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E14" t="s">
         <v>11</v>
@@ -10283,10 +10283,10 @@
         <v>309</v>
       </c>
       <c r="H14" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="I14" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="J14" t="s">
         <v>14</v>
@@ -10295,10 +10295,10 @@
         <v>309</v>
       </c>
       <c r="M14" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="N14" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="O14" t="s">
         <v>17</v>
@@ -10333,10 +10333,10 @@
         <v>309</v>
       </c>
       <c r="C15" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D15" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E15" t="s">
         <v>11</v>
@@ -10345,10 +10345,10 @@
         <v>309</v>
       </c>
       <c r="H15" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="I15" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="J15" t="s">
         <v>14</v>
@@ -10357,10 +10357,10 @@
         <v>309</v>
       </c>
       <c r="M15" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="N15" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="O15" t="s">
         <v>17</v>
@@ -10369,10 +10369,10 @@
         <v>309</v>
       </c>
       <c r="R15" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="S15" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="T15" t="s">
         <v>18</v>
@@ -10381,10 +10381,10 @@
         <v>309</v>
       </c>
       <c r="W15" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="X15" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="Y15" t="s">
         <v>19</v>
@@ -10407,10 +10407,10 @@
         <v>309</v>
       </c>
       <c r="H16" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="I16" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="J16" t="s">
         <v>14</v>
@@ -10419,10 +10419,10 @@
         <v>309</v>
       </c>
       <c r="M16" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="N16" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="O16" t="s">
         <v>17</v>
@@ -10431,10 +10431,10 @@
         <v>309</v>
       </c>
       <c r="R16" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="S16" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="T16" t="s">
         <v>18</v>
@@ -10443,10 +10443,10 @@
         <v>309</v>
       </c>
       <c r="W16" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="X16" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Y16" t="s">
         <v>19</v>
@@ -10457,10 +10457,10 @@
         <v>309</v>
       </c>
       <c r="C17" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D17" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E17" t="s">
         <v>11</v>
@@ -10469,10 +10469,10 @@
         <v>309</v>
       </c>
       <c r="H17" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="I17" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="J17" t="s">
         <v>14</v>
@@ -10543,10 +10543,10 @@
         <v>309</v>
       </c>
       <c r="M18" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="N18" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="O18" t="s">
         <v>17</v>
@@ -10555,10 +10555,10 @@
         <v>309</v>
       </c>
       <c r="R18" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="S18" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="T18" t="s">
         <v>18</v>
@@ -10567,10 +10567,10 @@
         <v>309</v>
       </c>
       <c r="W18" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="X18" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="Y18" t="s">
         <v>19</v>
@@ -10605,10 +10605,10 @@
         <v>309</v>
       </c>
       <c r="M19" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="N19" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="O19" t="s">
         <v>17</v>
@@ -10617,10 +10617,10 @@
         <v>309</v>
       </c>
       <c r="R19" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="S19" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="T19" t="s">
         <v>18</v>
@@ -10629,10 +10629,10 @@
         <v>309</v>
       </c>
       <c r="W19" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="X19" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="Y19" t="s">
         <v>19</v>
@@ -10643,10 +10643,10 @@
         <v>309</v>
       </c>
       <c r="C20" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D20" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E20" t="s">
         <v>11</v>
@@ -10655,10 +10655,10 @@
         <v>309</v>
       </c>
       <c r="H20" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="I20" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="J20" t="s">
         <v>14</v>
@@ -10667,10 +10667,10 @@
         <v>309</v>
       </c>
       <c r="M20" t="s">
-        <v>338</v>
+        <v>322</v>
       </c>
       <c r="N20" t="s">
-        <v>339</v>
+        <v>323</v>
       </c>
       <c r="O20" t="s">
         <v>17</v>
@@ -10729,10 +10729,10 @@
         <v>309</v>
       </c>
       <c r="M21" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="N21" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="O21" t="s">
         <v>17</v>
@@ -10741,10 +10741,10 @@
         <v>309</v>
       </c>
       <c r="R21" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="S21" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="T21" t="s">
         <v>18</v>
@@ -10753,10 +10753,10 @@
         <v>309</v>
       </c>
       <c r="W21" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="X21" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="Y21" t="s">
         <v>19</v>
@@ -10767,10 +10767,10 @@
         <v>309</v>
       </c>
       <c r="H22" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="I22" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="J22" t="s">
         <v>14</v>
@@ -10779,10 +10779,10 @@
         <v>309</v>
       </c>
       <c r="M22" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="N22" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="O22" t="s">
         <v>17</v>
@@ -10817,10 +10817,10 @@
         <v>309</v>
       </c>
       <c r="H23" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="I23" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="J23" t="s">
         <v>14</v>
@@ -10829,10 +10829,10 @@
         <v>309</v>
       </c>
       <c r="M23" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="N23" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="O23" t="s">
         <v>17</v>
@@ -10841,10 +10841,10 @@
         <v>309</v>
       </c>
       <c r="R23" t="s">
-        <v>314</v>
+        <v>342</v>
       </c>
       <c r="S23" t="s">
-        <v>315</v>
+        <v>343</v>
       </c>
       <c r="T23" t="s">
         <v>18</v>
@@ -10853,10 +10853,10 @@
         <v>309</v>
       </c>
       <c r="W23" t="s">
-        <v>314</v>
+        <v>342</v>
       </c>
       <c r="X23" t="s">
-        <v>315</v>
+        <v>343</v>
       </c>
       <c r="Y23" t="s">
         <v>19</v>
@@ -10867,10 +10867,10 @@
         <v>309</v>
       </c>
       <c r="H24" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="I24" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="J24" t="s">
         <v>14</v>
@@ -10879,10 +10879,10 @@
         <v>309</v>
       </c>
       <c r="M24" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="N24" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="O24" t="s">
         <v>17</v>
@@ -10893,10 +10893,10 @@
         <v>309</v>
       </c>
       <c r="H25" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="I25" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="J25" t="s">
         <v>14</v>
@@ -10905,10 +10905,10 @@
         <v>309</v>
       </c>
       <c r="M25" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="N25" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="O25" t="s">
         <v>17</v>
@@ -10919,10 +10919,10 @@
         <v>309</v>
       </c>
       <c r="H26" t="s">
-        <v>314</v>
+        <v>342</v>
       </c>
       <c r="I26" t="s">
-        <v>315</v>
+        <v>343</v>
       </c>
       <c r="J26" t="s">
         <v>14</v>
@@ -10931,10 +10931,10 @@
         <v>309</v>
       </c>
       <c r="M26" t="s">
-        <v>342</v>
+        <v>312</v>
       </c>
       <c r="N26" t="s">
-        <v>343</v>
+        <v>313</v>
       </c>
       <c r="O26" t="s">
         <v>17</v>
@@ -10945,10 +10945,10 @@
         <v>309</v>
       </c>
       <c r="H27" t="s">
-        <v>338</v>
+        <v>320</v>
       </c>
       <c r="I27" t="s">
-        <v>339</v>
+        <v>321</v>
       </c>
       <c r="J27" t="s">
         <v>14</v>
@@ -10957,10 +10957,10 @@
         <v>309</v>
       </c>
       <c r="M27" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="N27" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="O27" t="s">
         <v>17</v>
@@ -10972,7 +10972,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF25A2F-8AB6-447E-824D-795C14BA3F7D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E58C2133-B04F-4F5E-A811-50C870CF15AA}">
   <dimension ref="B2:C4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11003,7 +11003,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AF8A607-72FD-4C91-959F-0B8F36D964CC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5CA0EAE-4366-4949-BD9E-993ED3A9FDA5}">
   <dimension ref="B9:Y23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11115,10 +11115,10 @@
         <v>344</v>
       </c>
       <c r="M11" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="N11" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="O11" t="s">
         <v>17</v>
@@ -11153,10 +11153,10 @@
         <v>344</v>
       </c>
       <c r="C12" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D12" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
@@ -11165,10 +11165,10 @@
         <v>344</v>
       </c>
       <c r="H12" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="I12" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="J12" t="s">
         <v>14</v>
@@ -11177,10 +11177,10 @@
         <v>344</v>
       </c>
       <c r="M12" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="N12" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="O12" t="s">
         <v>17</v>
@@ -11189,10 +11189,10 @@
         <v>344</v>
       </c>
       <c r="R12" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="S12" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="T12" t="s">
         <v>18</v>
@@ -11201,10 +11201,10 @@
         <v>344</v>
       </c>
       <c r="W12" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="X12" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="Y12" t="s">
         <v>19</v>
@@ -11251,10 +11251,10 @@
         <v>344</v>
       </c>
       <c r="R13" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="S13" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="T13" t="s">
         <v>18</v>
@@ -11263,10 +11263,10 @@
         <v>344</v>
       </c>
       <c r="W13" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="X13" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="Y13" t="s">
         <v>19</v>
@@ -11277,10 +11277,10 @@
         <v>344</v>
       </c>
       <c r="C14" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D14" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E14" t="s">
         <v>11</v>
@@ -11289,10 +11289,10 @@
         <v>344</v>
       </c>
       <c r="H14" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="I14" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="J14" t="s">
         <v>14</v>
@@ -11301,10 +11301,10 @@
         <v>344</v>
       </c>
       <c r="M14" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="N14" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="O14" t="s">
         <v>17</v>
@@ -11313,10 +11313,10 @@
         <v>344</v>
       </c>
       <c r="R14" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="S14" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="T14" t="s">
         <v>18</v>
@@ -11325,10 +11325,10 @@
         <v>344</v>
       </c>
       <c r="W14" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="X14" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Y14" t="s">
         <v>19</v>
@@ -11339,10 +11339,10 @@
         <v>344</v>
       </c>
       <c r="C15" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D15" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E15" t="s">
         <v>11</v>
@@ -11351,10 +11351,10 @@
         <v>344</v>
       </c>
       <c r="H15" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="I15" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="J15" t="s">
         <v>14</v>
@@ -11363,10 +11363,10 @@
         <v>344</v>
       </c>
       <c r="M15" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="N15" t="s">
-        <v>368</v>
+        <v>348</v>
       </c>
       <c r="O15" t="s">
         <v>17</v>
@@ -11401,10 +11401,10 @@
         <v>344</v>
       </c>
       <c r="C16" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D16" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E16" t="s">
         <v>11</v>
@@ -11413,10 +11413,10 @@
         <v>344</v>
       </c>
       <c r="H16" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="I16" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="J16" t="s">
         <v>14</v>
@@ -11425,10 +11425,10 @@
         <v>344</v>
       </c>
       <c r="M16" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="N16" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="O16" t="s">
         <v>17</v>
@@ -11437,10 +11437,10 @@
         <v>344</v>
       </c>
       <c r="R16" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="S16" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="T16" t="s">
         <v>18</v>
@@ -11449,10 +11449,10 @@
         <v>344</v>
       </c>
       <c r="W16" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="X16" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="Y16" t="s">
         <v>19</v>
@@ -11463,10 +11463,10 @@
         <v>344</v>
       </c>
       <c r="C17" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D17" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E17" t="s">
         <v>11</v>
@@ -11475,10 +11475,10 @@
         <v>344</v>
       </c>
       <c r="H17" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="I17" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="J17" t="s">
         <v>14</v>
@@ -11487,10 +11487,10 @@
         <v>344</v>
       </c>
       <c r="M17" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="N17" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="O17" t="s">
         <v>17</v>
@@ -11499,10 +11499,10 @@
         <v>344</v>
       </c>
       <c r="R17" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="S17" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="T17" t="s">
         <v>18</v>
@@ -11511,10 +11511,10 @@
         <v>344</v>
       </c>
       <c r="W17" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="X17" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="Y17" t="s">
         <v>19</v>
@@ -11549,10 +11549,10 @@
         <v>344</v>
       </c>
       <c r="M18" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N18" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O18" t="s">
         <v>17</v>
@@ -11561,10 +11561,10 @@
         <v>344</v>
       </c>
       <c r="R18" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="S18" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="T18" t="s">
         <v>18</v>
@@ -11573,10 +11573,10 @@
         <v>344</v>
       </c>
       <c r="W18" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="X18" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="Y18" t="s">
         <v>19</v>
@@ -11587,10 +11587,10 @@
         <v>344</v>
       </c>
       <c r="C19" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="D19" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="E19" t="s">
         <v>11</v>
@@ -11611,10 +11611,10 @@
         <v>344</v>
       </c>
       <c r="M19" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="N19" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="O19" t="s">
         <v>17</v>
@@ -11661,10 +11661,10 @@
         <v>344</v>
       </c>
       <c r="H20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="I20" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J20" t="s">
         <v>14</v>
@@ -11673,10 +11673,10 @@
         <v>344</v>
       </c>
       <c r="M20" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="N20" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="O20" t="s">
         <v>17</v>
@@ -11723,10 +11723,10 @@
         <v>344</v>
       </c>
       <c r="H21" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="I21" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="J21" t="s">
         <v>14</v>
@@ -11735,10 +11735,10 @@
         <v>344</v>
       </c>
       <c r="M21" t="s">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="N21" t="s">
-        <v>350</v>
+        <v>368</v>
       </c>
       <c r="O21" t="s">
         <v>17</v>
@@ -11747,10 +11747,10 @@
         <v>344</v>
       </c>
       <c r="R21" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="S21" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="T21" t="s">
         <v>18</v>
@@ -11759,10 +11759,10 @@
         <v>344</v>
       </c>
       <c r="W21" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="X21" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Y21" t="s">
         <v>19</v>
@@ -11785,10 +11785,10 @@
         <v>344</v>
       </c>
       <c r="M22" t="s">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="N22" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="O22" t="s">
         <v>17</v>
@@ -11799,10 +11799,10 @@
         <v>344</v>
       </c>
       <c r="M23" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="N23" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="O23" t="s">
         <v>17</v>
